--- a/research/traditional_assets/database/data/france/france_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/france/france_semiconductor.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00508</v>
+        <v>-0.0295</v>
       </c>
       <c r="G2">
-        <v>-0.06739010989010985</v>
+        <v>0.03999493414387027</v>
       </c>
       <c r="H2">
-        <v>-0.5401373626373626</v>
+        <v>-0.5055977710233029</v>
       </c>
       <c r="I2">
-        <v>-0.7473076923076923</v>
+        <v>-0.6252786220871327</v>
       </c>
       <c r="J2">
-        <v>-0.7473076923076923</v>
+        <v>-0.5393485190517665</v>
       </c>
       <c r="K2">
-        <v>-23.952</v>
+        <v>-21.846</v>
       </c>
       <c r="L2">
-        <v>-0.6580219780219781</v>
+        <v>-0.5533434650455926</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.81</v>
+        <v>12.534</v>
       </c>
       <c r="V2">
-        <v>0.09784671532846716</v>
+        <v>0.07109472490073739</v>
       </c>
       <c r="W2">
-        <v>-0.02360655737704918</v>
+        <v>-0.03714285714285714</v>
       </c>
       <c r="X2">
-        <v>0.1169689054680913</v>
+        <v>0.194856960268503</v>
       </c>
       <c r="Y2">
-        <v>-0.1405754628451404</v>
+        <v>-0.2319998174113602</v>
       </c>
       <c r="Z2">
-        <v>0.5123873873873874</v>
+        <v>0.5344524164072019</v>
       </c>
       <c r="AA2">
-        <v>-0.2651448639157155</v>
+        <v>-0.1829111206526406</v>
       </c>
       <c r="AB2">
-        <v>0.08401131841827232</v>
+        <v>0.144926427462394</v>
       </c>
       <c r="AC2">
-        <v>-0.3698212220816561</v>
+        <v>-0.3273051356536562</v>
       </c>
       <c r="AD2">
-        <v>79.18000000000001</v>
+        <v>46.48999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>79.18000000000001</v>
+        <v>46.48999999999999</v>
       </c>
       <c r="AG2">
-        <v>52.37</v>
+        <v>33.956</v>
       </c>
       <c r="AH2">
-        <v>0.2241916303301433</v>
+        <v>0.2086718434400108</v>
       </c>
       <c r="AI2">
-        <v>0.8032055183607222</v>
+        <v>0.5798204040907957</v>
       </c>
       <c r="AJ2">
-        <v>0.1604620522719613</v>
+        <v>0.1614983638992466</v>
       </c>
       <c r="AK2">
-        <v>0.7296920718963354</v>
+        <v>0.5019661177305385</v>
       </c>
       <c r="AL2">
-        <v>0.843</v>
+        <v>0.75</v>
       </c>
       <c r="AM2">
-        <v>0.843</v>
+        <v>0.579</v>
       </c>
       <c r="AN2">
-        <v>-3.849856566344144</v>
+        <v>-2.681857513700605</v>
       </c>
       <c r="AO2">
-        <v>-32.26809015421115</v>
+        <v>-32.91466666666667</v>
       </c>
       <c r="AP2">
-        <v>-2.54631205328925</v>
+        <v>-1.958811652725699</v>
       </c>
       <c r="AQ2">
-        <v>-32.26809015421115</v>
+        <v>-42.63557858376512</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00508</v>
+        <v>-0.0295</v>
       </c>
       <c r="G3">
-        <v>0.1455905511811024</v>
+        <v>0.1961377870563674</v>
       </c>
       <c r="H3">
-        <v>0.01094488188976378</v>
+        <v>0.0009394572025052192</v>
       </c>
       <c r="I3">
-        <v>-0.04425196850393701</v>
+        <v>-0.03402922755741127</v>
       </c>
       <c r="J3">
-        <v>-0.04425196850393701</v>
+        <v>-0.01999963373988206</v>
       </c>
       <c r="K3">
-        <v>-0.432</v>
+        <v>-0.676</v>
       </c>
       <c r="L3">
-        <v>-0.03401574803149606</v>
+        <v>-0.07056367432150314</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,67 +764,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.02360655737704918</v>
+        <v>-0.03714285714285714</v>
       </c>
       <c r="X3">
-        <v>0.1169689054680913</v>
+        <v>0.194856960268503</v>
       </c>
       <c r="Y3">
-        <v>-0.1405754628451404</v>
+        <v>-0.2319998174113602</v>
       </c>
       <c r="Z3">
-        <v>0.4911059551430781</v>
+        <v>0.3789556962025316</v>
       </c>
       <c r="AA3">
-        <v>-0.0217324052590874</v>
+        <v>-0.007578975127692651</v>
       </c>
       <c r="AB3">
-        <v>0.08102487229388369</v>
+        <v>0.144926427462394</v>
       </c>
       <c r="AC3">
-        <v>-0.1027572775529711</v>
+        <v>-0.1525054025900867</v>
       </c>
       <c r="AD3">
-        <v>7.08</v>
+        <v>5.59</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.08</v>
+        <v>5.59</v>
       </c>
       <c r="AG3">
-        <v>7.08</v>
+        <v>5.59</v>
       </c>
       <c r="AH3">
-        <v>0.3852013057671381</v>
+        <v>0.3349310964649491</v>
       </c>
       <c r="AI3">
-        <v>0.2800632911392405</v>
+        <v>0.2782478845196615</v>
       </c>
       <c r="AJ3">
-        <v>0.3852013057671381</v>
+        <v>0.3349310964649491</v>
       </c>
       <c r="AK3">
-        <v>0.2800632911392405</v>
+        <v>0.2782478845196615</v>
       </c>
       <c r="AL3">
-        <v>0.065</v>
+        <v>0.153</v>
       </c>
       <c r="AM3">
-        <v>0.065</v>
+        <v>-0.01800000000000002</v>
       </c>
       <c r="AN3">
-        <v>30.3862660944206</v>
+        <v>14.90666666666667</v>
       </c>
       <c r="AO3">
-        <v>-8.646153846153847</v>
+        <v>-2.130718954248366</v>
       </c>
       <c r="AP3">
-        <v>30.3862660944206</v>
+        <v>14.90666666666667</v>
       </c>
       <c r="AQ3">
-        <v>-8.646153846153847</v>
+        <v>18.1111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -844,22 +844,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.4309230769230769</v>
+        <v>-0.1205673758865248</v>
       </c>
       <c r="H4">
-        <v>-0.4692307692307692</v>
+        <v>-0.274468085106383</v>
       </c>
       <c r="I4">
-        <v>-0.4646153846153846</v>
+        <v>-0.3021276595744681</v>
       </c>
       <c r="J4">
-        <v>-0.4646153846153846</v>
+        <v>-0.3021276595744681</v>
       </c>
       <c r="K4">
-        <v>-6.72</v>
+        <v>-5.47</v>
       </c>
       <c r="L4">
-        <v>-0.5169230769230769</v>
+        <v>-0.3879432624113475</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.51</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="V4">
-        <v>0.0859047619047619</v>
+        <v>0.02152073732718894</v>
       </c>
       <c r="W4">
-        <v>0.2847457627118644</v>
+        <v>0.1811258278145695</v>
       </c>
       <c r="X4">
-        <v>0.1414846484326306</v>
+        <v>0.1998360344693073</v>
       </c>
       <c r="Y4">
-        <v>0.1432611142792337</v>
+        <v>-0.01871020665473774</v>
       </c>
       <c r="Z4">
-        <v>0.5706760316066725</v>
+        <v>0.605410047230571</v>
       </c>
       <c r="AA4">
-        <v>-0.2651448639157155</v>
+        <v>-0.1829111206526406</v>
       </c>
       <c r="AB4">
-        <v>0.1046763581659406</v>
+        <v>0.1443940150010155</v>
       </c>
       <c r="AC4">
-        <v>-0.3698212220816561</v>
+        <v>-0.3273051356536562</v>
       </c>
       <c r="AD4">
-        <v>58</v>
+        <v>24.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>58</v>
+        <v>24.4</v>
       </c>
       <c r="AG4">
-        <v>53.49</v>
+        <v>23.466</v>
       </c>
       <c r="AH4">
-        <v>0.5248868778280543</v>
+        <v>0.359882005899705</v>
       </c>
       <c r="AI4">
-        <v>2.2568093385214</v>
+        <v>1.436138905238376</v>
       </c>
       <c r="AJ4">
-        <v>0.5046702519105576</v>
+        <v>0.3509406873448389</v>
       </c>
       <c r="AK4">
-        <v>2.524303916941953</v>
+        <v>1.461509715994021</v>
       </c>
       <c r="AL4">
-        <v>0.644</v>
+        <v>0.46</v>
       </c>
       <c r="AM4">
-        <v>0.644</v>
+        <v>0.46</v>
       </c>
       <c r="AN4">
-        <v>-11.83673469387755</v>
+        <v>-9.003690036900368</v>
       </c>
       <c r="AO4">
-        <v>-9.378881987577639</v>
+        <v>-9.260869565217391</v>
       </c>
       <c r="AP4">
-        <v>-10.91632653061224</v>
+        <v>-8.659040590405903</v>
       </c>
       <c r="AQ4">
-        <v>-9.378881987577639</v>
+        <v>-9.260869565217391</v>
       </c>
     </row>
     <row r="5">
@@ -969,22 +969,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1214953271028038</v>
+        <v>0.08860759493670876</v>
       </c>
       <c r="H5">
-        <v>-1.280373831775701</v>
+        <v>-1.018987341772152</v>
       </c>
       <c r="I5">
-        <v>-1.925233644859813</v>
+        <v>-1.272151898734177</v>
       </c>
       <c r="J5">
-        <v>-1.925233644859813</v>
+        <v>-1.272151898734177</v>
       </c>
       <c r="K5">
-        <v>-16.8</v>
+        <v>-15.7</v>
       </c>
       <c r="L5">
-        <v>-1.570093457943925</v>
+        <v>-0.9936708860759492</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,73 +1008,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>22.3</v>
+        <v>11.6</v>
       </c>
       <c r="V5">
-        <v>0.1060894386298763</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="W5">
-        <v>-0.5090909090909091</v>
+        <v>-0.4686567164179104</v>
       </c>
       <c r="X5">
-        <v>0.08828752561045229</v>
+        <v>0.1635820018391733</v>
       </c>
       <c r="Y5">
-        <v>-0.5973784347013614</v>
+        <v>-0.6322387182570837</v>
       </c>
       <c r="Z5">
-        <v>0.4776785714285715</v>
+        <v>0.624505928853755</v>
       </c>
       <c r="AA5">
-        <v>-0.9196428571428573</v>
+        <v>-0.7944664031620554</v>
       </c>
       <c r="AB5">
-        <v>0.08401131841827232</v>
+        <v>0.1495275248639928</v>
       </c>
       <c r="AC5">
-        <v>-1.00365417556113</v>
+        <v>-0.9439939280260483</v>
       </c>
       <c r="AD5">
-        <v>14.1</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14.1</v>
+        <v>16.5</v>
       </c>
       <c r="AG5">
-        <v>-8.200000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AH5">
-        <v>0.06286223807400802</v>
+        <v>0.1193058568329718</v>
       </c>
       <c r="AI5">
-        <v>0.296218487394958</v>
+        <v>0.382830626450116</v>
       </c>
       <c r="AJ5">
-        <v>-0.0405940594059406</v>
+        <v>0.03867403314917128</v>
       </c>
       <c r="AK5">
-        <v>-0.324110671936759</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="AL5">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="AM5">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="AN5">
-        <v>-0.8867924528301886</v>
+        <v>-1.1</v>
       </c>
       <c r="AO5">
-        <v>-153.7313432835821</v>
+        <v>-146.7153284671533</v>
       </c>
       <c r="AP5">
-        <v>0.5157232704402517</v>
+        <v>-0.3266666666666667</v>
       </c>
       <c r="AQ5">
-        <v>-153.7313432835821</v>
+        <v>-146.7153284671533</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/france/france_semiconductor.xlsx
@@ -1522,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1659,22 +1659,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1307400749243579</v>
+        <v>0.130446974737047</v>
       </c>
       <c r="C2">
-        <v>48.46080478370808</v>
+        <v>48.11214553839461</v>
       </c>
       <c r="D2">
-        <v>48.32780478370808</v>
+        <v>48.4951455383946</v>
       </c>
       <c r="E2">
-        <v>-13.9</v>
+        <v>-13.384</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="G2">
         <v>0.133</v>
@@ -1695,28 +1695,28 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0259548</v>
       </c>
       <c r="N2">
-        <v>0.6733333333333336</v>
+        <v>0.6473785333333335</v>
       </c>
       <c r="O2">
-        <v>0.1683333333333334</v>
+        <v>0.1618446333333334</v>
       </c>
       <c r="P2">
-        <v>0.5050000000000001</v>
+        <v>0.4855339000000001</v>
       </c>
       <c r="Q2">
-        <v>1.665</v>
+        <v>1.6455339</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1307400749243579</v>
+        <v>0.1313835603404515</v>
       </c>
       <c r="T2">
-        <v>1.655640159154052</v>
+        <v>1.668182887632492</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>25.94253599847941</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1741,22 +1741,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.130446974737047</v>
+        <v>0.1301538745497361</v>
       </c>
       <c r="C3">
-        <v>48.11214553839461</v>
+        <v>47.76464919417622</v>
       </c>
       <c r="D3">
-        <v>48.4951455383946</v>
+        <v>48.66364919417621</v>
       </c>
       <c r="E3">
-        <v>-13.384</v>
+        <v>-12.868</v>
       </c>
       <c r="F3">
-        <v>0.516</v>
+        <v>1.032</v>
       </c>
       <c r="G3">
         <v>0.133</v>
@@ -1777,28 +1777,28 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M3">
-        <v>0.0259548</v>
+        <v>0.0519096</v>
       </c>
       <c r="N3">
-        <v>0.6473785333333335</v>
+        <v>0.6214237333333336</v>
       </c>
       <c r="O3">
-        <v>0.1618446333333334</v>
+        <v>0.1553559333333334</v>
       </c>
       <c r="P3">
-        <v>0.4855339000000001</v>
+        <v>0.4660678000000001</v>
       </c>
       <c r="Q3">
-        <v>1.6455339</v>
+        <v>1.6260678</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1313835603404515</v>
+        <v>0.1320401781119756</v>
       </c>
       <c r="T3">
-        <v>1.668182887632492</v>
+        <v>1.680981590161512</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>25.94253599847941</v>
+        <v>12.97126799923971</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1301538745497361</v>
+        <v>0.1299327743624252</v>
       </c>
       <c r="C4">
-        <v>47.76464919417622</v>
+        <v>47.3765368340835</v>
       </c>
       <c r="D4">
-        <v>48.66364919417621</v>
+        <v>48.7915368340835</v>
       </c>
       <c r="E4">
-        <v>-12.868</v>
+        <v>-12.352</v>
       </c>
       <c r="F4">
-        <v>1.032</v>
+        <v>1.548</v>
       </c>
       <c r="G4">
         <v>0.133</v>
@@ -1859,45 +1859,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M4">
-        <v>0.0519096</v>
+        <v>0.082818</v>
       </c>
       <c r="N4">
-        <v>0.6214237333333336</v>
+        <v>0.5905153333333335</v>
       </c>
       <c r="O4">
-        <v>0.1553559333333334</v>
+        <v>0.1476288333333334</v>
       </c>
       <c r="P4">
-        <v>0.4660678000000001</v>
+        <v>0.4428865000000001</v>
       </c>
       <c r="Q4">
-        <v>1.6260678</v>
+        <v>1.6028865</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1320401781119756</v>
+        <v>0.1327103343942528</v>
       </c>
       <c r="T4">
-        <v>1.680981590161512</v>
+        <v>1.694044183464326</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>12.97126799923971</v>
+        <v>8.130277636906634</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1905,22 +1905,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1299327743624252</v>
+        <v>0.1297176741751143</v>
       </c>
       <c r="C5">
-        <v>47.3765368340835</v>
+        <v>46.98560069953691</v>
       </c>
       <c r="D5">
-        <v>48.7915368340835</v>
+        <v>48.91660069953691</v>
       </c>
       <c r="E5">
-        <v>-12.352</v>
+        <v>-11.836</v>
       </c>
       <c r="F5">
-        <v>1.548</v>
+        <v>2.064</v>
       </c>
       <c r="G5">
         <v>0.133</v>
@@ -1941,45 +1941,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M5">
-        <v>0.082818</v>
+        <v>0.1141392</v>
       </c>
       <c r="N5">
-        <v>0.5905153333333335</v>
+        <v>0.5591941333333336</v>
       </c>
       <c r="O5">
-        <v>0.1476288333333334</v>
+        <v>0.1397985333333334</v>
       </c>
       <c r="P5">
-        <v>0.4428865000000001</v>
+        <v>0.4193956000000002</v>
       </c>
       <c r="Q5">
-        <v>1.6028865</v>
+        <v>1.5793956</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1327103343942528</v>
+        <v>0.133394452265744</v>
       </c>
       <c r="T5">
-        <v>1.694044183464326</v>
+        <v>1.707378914127616</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.040125</v>
+        <v>0.041475</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.130277636906634</v>
+        <v>5.899229478858565</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1987,22 +1987,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1297176741751143</v>
+        <v>0.1294620739878034</v>
       </c>
       <c r="C6">
-        <v>46.98560069953691</v>
+        <v>46.6190482533142</v>
       </c>
       <c r="D6">
-        <v>48.91660069953691</v>
+        <v>49.06604825331419</v>
       </c>
       <c r="E6">
-        <v>-11.836</v>
+        <v>-11.32</v>
       </c>
       <c r="F6">
-        <v>2.064</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
         <v>0.133</v>
@@ -2023,28 +2023,28 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M6">
-        <v>0.1141392</v>
+        <v>0.142674</v>
       </c>
       <c r="N6">
-        <v>0.5591941333333336</v>
+        <v>0.5306593333333336</v>
       </c>
       <c r="O6">
-        <v>0.1397985333333334</v>
+        <v>0.1326648333333334</v>
       </c>
       <c r="P6">
-        <v>0.4193956000000002</v>
+        <v>0.3979945000000002</v>
       </c>
       <c r="Q6">
-        <v>1.5793956</v>
+        <v>1.5579945</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.133394452265744</v>
+        <v>0.1340929726187404</v>
       </c>
       <c r="T6">
-        <v>1.707378914127616</v>
+        <v>1.720994375962765</v>
       </c>
       <c r="U6">
         <v>0.0553</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>5.899229478858565</v>
+        <v>4.719383583086852</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2069,22 +2069,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1294620739878034</v>
+        <v>0.1294764738004925</v>
       </c>
       <c r="C7">
-        <v>46.6190482533142</v>
+        <v>46.09460451910611</v>
       </c>
       <c r="D7">
-        <v>49.06604825331419</v>
+        <v>49.05760451910611</v>
       </c>
       <c r="E7">
-        <v>-11.32</v>
+        <v>-10.804</v>
       </c>
       <c r="F7">
-        <v>2.58</v>
+        <v>3.096000000000001</v>
       </c>
       <c r="G7">
         <v>0.133</v>
@@ -2105,45 +2105,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M7">
-        <v>0.142674</v>
+        <v>0.1897848</v>
       </c>
       <c r="N7">
-        <v>0.5306593333333336</v>
+        <v>0.4835485333333335</v>
       </c>
       <c r="O7">
-        <v>0.1326648333333334</v>
+        <v>0.1208871333333334</v>
       </c>
       <c r="P7">
-        <v>0.3979945000000002</v>
+        <v>0.3626614000000001</v>
       </c>
       <c r="Q7">
-        <v>1.5579945</v>
+        <v>1.5226614</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1340929726187404</v>
+        <v>0.1348063551069069</v>
       </c>
       <c r="T7">
-        <v>1.720994375962765</v>
+        <v>1.734899528475257</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.041475</v>
+        <v>0.045975</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.719383583086852</v>
+        <v>3.5478780878834</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2151,22 +2151,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1294764738004925</v>
+        <v>0.1298223736131816</v>
       </c>
       <c r="C8">
-        <v>46.09460451910611</v>
+        <v>45.37664621342604</v>
       </c>
       <c r="D8">
-        <v>49.05760451910611</v>
+        <v>48.85564621342604</v>
       </c>
       <c r="E8">
-        <v>-10.804</v>
+        <v>-10.288</v>
       </c>
       <c r="F8">
-        <v>3.096</v>
+        <v>3.612</v>
       </c>
       <c r="G8">
         <v>0.133</v>
@@ -2187,45 +2187,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M8">
-        <v>0.1897848</v>
+        <v>0.2597028</v>
       </c>
       <c r="N8">
-        <v>0.4835485333333336</v>
+        <v>0.4136305333333335</v>
       </c>
       <c r="O8">
-        <v>0.1208871333333334</v>
+        <v>0.1034076333333334</v>
       </c>
       <c r="P8">
-        <v>0.3626614000000002</v>
+        <v>0.3102229000000002</v>
       </c>
       <c r="Q8">
-        <v>1.5226614</v>
+        <v>1.4702229</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1348063551069069</v>
+        <v>0.1355350791539587</v>
       </c>
       <c r="T8">
-        <v>1.734899528475257</v>
+        <v>1.749103716525652</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.045975</v>
+        <v>0.053925</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.5478780878834</v>
+        <v>2.592707253573445</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2233,22 +2233,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1298223736131816</v>
+        <v>0.1299252734258707</v>
       </c>
       <c r="C9">
-        <v>45.37664621342606</v>
+        <v>44.80088727726525</v>
       </c>
       <c r="D9">
-        <v>48.85564621342606</v>
+        <v>48.79588727726524</v>
       </c>
       <c r="E9">
-        <v>-10.288</v>
+        <v>-9.771999999999998</v>
       </c>
       <c r="F9">
-        <v>3.612000000000001</v>
+        <v>4.128</v>
       </c>
       <c r="G9">
         <v>0.133</v>
@@ -2269,45 +2269,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M9">
-        <v>0.2597028000000001</v>
+        <v>0.3129024</v>
       </c>
       <c r="N9">
-        <v>0.4136305333333335</v>
+        <v>0.3604309333333335</v>
       </c>
       <c r="O9">
-        <v>0.1034076333333334</v>
+        <v>0.09010773333333338</v>
       </c>
       <c r="P9">
-        <v>0.3102229000000001</v>
+        <v>0.2703232000000002</v>
       </c>
       <c r="Q9">
-        <v>1.4702229</v>
+        <v>1.4303232</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1355350791539587</v>
+        <v>0.1362796450281203</v>
       </c>
       <c r="T9">
-        <v>1.749103716525652</v>
+        <v>1.763616691272795</v>
       </c>
       <c r="U9">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.592707253573444</v>
+        <v>2.151895713594186</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1299252734258707</v>
+        <v>0.1307819232385598</v>
       </c>
       <c r="C10">
-        <v>44.80088727726525</v>
+        <v>43.79300634420229</v>
       </c>
       <c r="D10">
-        <v>48.79588727726524</v>
+        <v>48.30400634420229</v>
       </c>
       <c r="E10">
-        <v>-9.771999999999998</v>
+        <v>-9.255999999999998</v>
       </c>
       <c r="F10">
-        <v>4.128</v>
+        <v>4.644</v>
       </c>
       <c r="G10">
         <v>0.133</v>
@@ -2351,45 +2351,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M10">
-        <v>0.3129024</v>
+        <v>0.41796</v>
       </c>
       <c r="N10">
-        <v>0.3604309333333335</v>
+        <v>0.2553733333333336</v>
       </c>
       <c r="O10">
-        <v>0.09010773333333338</v>
+        <v>0.06384333333333339</v>
       </c>
       <c r="P10">
-        <v>0.2703232000000002</v>
+        <v>0.1915300000000002</v>
       </c>
       <c r="Q10">
-        <v>1.4303232</v>
+        <v>1.35153</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1362796450281203</v>
+        <v>0.1370405749874284</v>
       </c>
       <c r="T10">
-        <v>1.763616691272795</v>
+        <v>1.778448632497896</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.151895713594186</v>
+        <v>1.610999457683351</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2397,22 +2397,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1307819232385598</v>
+        <v>0.1356902138996375</v>
       </c>
       <c r="C11">
-        <v>43.79300634420229</v>
+        <v>40.63945445789129</v>
       </c>
       <c r="D11">
-        <v>48.30400634420229</v>
+        <v>45.66645445789129</v>
       </c>
       <c r="E11">
-        <v>-9.255999999999998</v>
+        <v>-8.739999999999998</v>
       </c>
       <c r="F11">
-        <v>4.644</v>
+        <v>5.16</v>
       </c>
       <c r="G11">
         <v>0.133</v>
@@ -2433,45 +2433,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M11">
-        <v>0.41796</v>
+        <v>0.7574880000000001</v>
       </c>
       <c r="N11">
-        <v>0.2553733333333336</v>
+        <v>-0.08415466666666649</v>
       </c>
       <c r="O11">
-        <v>0.06384333333333339</v>
+        <v>-0.02103866666666662</v>
       </c>
       <c r="P11">
-        <v>0.1915300000000002</v>
+        <v>-0.06311599999999987</v>
       </c>
       <c r="Q11">
-        <v>1.35153</v>
+        <v>1.096884</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1370405749874284</v>
+        <v>0.138080542001607</v>
       </c>
       <c r="T11">
-        <v>1.778448632497896</v>
+        <v>1.798719525293824</v>
       </c>
       <c r="U11">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V11">
-        <v>0.25</v>
+        <v>0.2222257426300263</v>
       </c>
       <c r="W11">
-        <v>0.0675</v>
+        <v>0.1141772609819122</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y11">
-        <v>1.610999457683351</v>
+        <v>0.8889029705201053</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2479,22 +2479,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1356902138996375</v>
+        <v>0.1367002138996375</v>
       </c>
       <c r="C12">
-        <v>40.63945445789129</v>
+        <v>39.61605060234708</v>
       </c>
       <c r="D12">
-        <v>45.66645445789129</v>
+        <v>45.15905060234708</v>
       </c>
       <c r="E12">
-        <v>-8.739999999999998</v>
+        <v>-8.223999999999998</v>
       </c>
       <c r="F12">
-        <v>5.16</v>
+        <v>5.676</v>
       </c>
       <c r="G12">
         <v>0.133</v>
@@ -2515,37 +2515,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M12">
-        <v>0.7574880000000001</v>
+        <v>0.8332368000000001</v>
       </c>
       <c r="N12">
-        <v>-0.08415466666666649</v>
+        <v>-0.1599034666666665</v>
       </c>
       <c r="O12">
-        <v>-0.02103866666666662</v>
+        <v>-0.03997586666666664</v>
       </c>
       <c r="P12">
-        <v>-0.06311599999999987</v>
+        <v>-0.1199275999999999</v>
       </c>
       <c r="Q12">
-        <v>1.096884</v>
+        <v>1.0400724</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.138080542001607</v>
+        <v>0.139117402024097</v>
       </c>
       <c r="T12">
-        <v>1.798719525293824</v>
+        <v>1.818929857038698</v>
       </c>
       <c r="U12">
         <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.2222257426300263</v>
+        <v>0.202023402390933</v>
       </c>
       <c r="W12">
-        <v>0.1141772609819122</v>
+        <v>0.117142964529011</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.8889029705201053</v>
+        <v>0.808093609563732</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1367002138996375</v>
+        <v>0.1446978319506197</v>
       </c>
       <c r="C13">
-        <v>39.61605060234708</v>
+        <v>35.44815216191533</v>
       </c>
       <c r="D13">
-        <v>45.15905060234708</v>
+        <v>41.50715216191533</v>
       </c>
       <c r="E13">
-        <v>-8.223999999999998</v>
+        <v>-7.707999999999998</v>
       </c>
       <c r="F13">
-        <v>5.676</v>
+        <v>6.192</v>
       </c>
       <c r="G13">
         <v>0.133</v>
@@ -2597,45 +2597,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M13">
-        <v>0.8332368000000001</v>
+        <v>1.2433536</v>
       </c>
       <c r="N13">
-        <v>-0.1599034666666665</v>
+        <v>-0.5700202666666665</v>
       </c>
       <c r="O13">
-        <v>-0.03997586666666664</v>
+        <v>-0.1425050666666666</v>
       </c>
       <c r="P13">
-        <v>-0.1199275999999999</v>
+        <v>-0.4275151999999999</v>
       </c>
       <c r="Q13">
-        <v>1.0400724</v>
+        <v>0.7324848</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.139117402024097</v>
+        <v>0.140754665741396</v>
       </c>
       <c r="T13">
-        <v>1.818929857038698</v>
+        <v>1.850843174326211</v>
       </c>
       <c r="U13">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.202023402390933</v>
+        <v>0.1353865331095944</v>
       </c>
       <c r="W13">
-        <v>0.117142964529011</v>
+        <v>0.1736143841515935</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.808093609563732</v>
+        <v>0.5415461324383776</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2643,22 +2643,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1446978319506197</v>
+        <v>0.1510026619655371</v>
       </c>
       <c r="C14">
-        <v>35.44815216191533</v>
+        <v>32.44461492763968</v>
       </c>
       <c r="D14">
-        <v>41.50715216191533</v>
+        <v>39.01961492763968</v>
       </c>
       <c r="E14">
-        <v>-7.707999999999998</v>
+        <v>-7.191999999999998</v>
       </c>
       <c r="F14">
-        <v>6.192</v>
+        <v>6.708</v>
       </c>
       <c r="G14">
         <v>0.133</v>
@@ -2679,45 +2679,45 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M14">
-        <v>1.2433536</v>
+        <v>1.5817464</v>
       </c>
       <c r="N14">
-        <v>-0.5700202666666665</v>
+        <v>-0.9084130666666665</v>
       </c>
       <c r="O14">
-        <v>-0.1425050666666666</v>
+        <v>-0.2271032666666666</v>
       </c>
       <c r="P14">
-        <v>-0.4275151999999999</v>
+        <v>-0.6813098</v>
       </c>
       <c r="Q14">
-        <v>0.7324848</v>
+        <v>0.4786902</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.140754665741396</v>
+        <v>0.1420815354797079</v>
       </c>
       <c r="T14">
-        <v>1.850843174326211</v>
+        <v>1.876706335227256</v>
       </c>
       <c r="U14">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.1353865331095944</v>
+        <v>0.1064224538986359</v>
       </c>
       <c r="W14">
-        <v>0.1736143841515935</v>
+        <v>0.2107055853707017</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.5415461324383776</v>
+        <v>0.4256898155945438</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2725,22 +2725,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1510026619655371</v>
+        <v>0.1529026619655371</v>
       </c>
       <c r="C15">
-        <v>32.44461492763968</v>
+        <v>31.23640740448427</v>
       </c>
       <c r="D15">
-        <v>39.01961492763968</v>
+        <v>38.32740740448427</v>
       </c>
       <c r="E15">
-        <v>-7.191999999999998</v>
+        <v>-6.675999999999997</v>
       </c>
       <c r="F15">
-        <v>6.708</v>
+        <v>7.224000000000001</v>
       </c>
       <c r="G15">
         <v>0.133</v>
@@ -2761,37 +2761,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M15">
-        <v>1.5817464</v>
+        <v>1.7034192</v>
       </c>
       <c r="N15">
-        <v>-0.9084130666666665</v>
+        <v>-1.030085866666667</v>
       </c>
       <c r="O15">
-        <v>-0.2271032666666666</v>
+        <v>-0.2575214666666667</v>
       </c>
       <c r="P15">
-        <v>-0.6813098</v>
+        <v>-0.7725644</v>
       </c>
       <c r="Q15">
-        <v>0.4786902</v>
+        <v>0.3874355999999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1420815354797079</v>
+        <v>0.1432010882178441</v>
       </c>
       <c r="T15">
-        <v>1.876706335227256</v>
+        <v>1.898528501915945</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.1064224538986359</v>
+        <v>0.09882085004873337</v>
       </c>
       <c r="W15">
-        <v>0.2107055853707017</v>
+        <v>0.2124980435585087</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.4256898155945438</v>
+        <v>0.3952834001949335</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2807,22 +2807,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1529026619655371</v>
+        <v>0.1548026619655371</v>
       </c>
       <c r="C16">
-        <v>31.23640740448427</v>
+        <v>30.05233129739302</v>
       </c>
       <c r="D16">
-        <v>38.32740740448427</v>
+        <v>37.65933129739302</v>
       </c>
       <c r="E16">
-        <v>-6.675999999999997</v>
+        <v>-6.159999999999997</v>
       </c>
       <c r="F16">
-        <v>7.224000000000001</v>
+        <v>7.740000000000001</v>
       </c>
       <c r="G16">
         <v>0.133</v>
@@ -2843,37 +2843,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M16">
-        <v>1.7034192</v>
+        <v>1.825092</v>
       </c>
       <c r="N16">
-        <v>-1.030085866666667</v>
+        <v>-1.151758666666667</v>
       </c>
       <c r="O16">
-        <v>-0.2575214666666667</v>
+        <v>-0.2879396666666667</v>
       </c>
       <c r="P16">
-        <v>-0.7725644</v>
+        <v>-0.8638190000000001</v>
       </c>
       <c r="Q16">
-        <v>0.3874355999999999</v>
+        <v>0.2961809999999998</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1432010882178441</v>
+        <v>0.1443469833733481</v>
       </c>
       <c r="T16">
-        <v>1.898528501915945</v>
+        <v>1.92086413135025</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.09882085004873337</v>
+        <v>0.0922327933788178</v>
       </c>
       <c r="W16">
-        <v>0.2124980435585087</v>
+        <v>0.2140515073212748</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3952834001949335</v>
+        <v>0.3689311735152713</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2889,22 +2889,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1548026619655371</v>
+        <v>0.1567026619655371</v>
       </c>
       <c r="C17">
-        <v>30.05233129739302</v>
+        <v>28.89114633792576</v>
       </c>
       <c r="D17">
-        <v>37.65933129739302</v>
+        <v>37.01414633792576</v>
       </c>
       <c r="E17">
-        <v>-6.159999999999998</v>
+        <v>-5.643999999999998</v>
       </c>
       <c r="F17">
-        <v>7.74</v>
+        <v>8.256</v>
       </c>
       <c r="G17">
         <v>0.133</v>
@@ -2925,37 +2925,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M17">
-        <v>1.825092</v>
+        <v>1.9467648</v>
       </c>
       <c r="N17">
-        <v>-1.151758666666667</v>
+        <v>-1.273431466666667</v>
       </c>
       <c r="O17">
-        <v>-0.2879396666666666</v>
+        <v>-0.3183578666666667</v>
       </c>
       <c r="P17">
-        <v>-0.8638189999999999</v>
+        <v>-0.9550736</v>
       </c>
       <c r="Q17">
-        <v>0.296181</v>
+        <v>0.2049264</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1443469833733481</v>
+        <v>0.1455201617468404</v>
       </c>
       <c r="T17">
-        <v>1.92086413135025</v>
+        <v>1.943731561485372</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.09223279337881782</v>
+        <v>0.0864682437926417</v>
       </c>
       <c r="W17">
-        <v>0.2140515073212748</v>
+        <v>0.2154107881136951</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3689311735152713</v>
+        <v>0.3458729751705668</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2971,22 +2971,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1567026619655371</v>
+        <v>0.1586026619655371</v>
       </c>
       <c r="C18">
-        <v>28.89114633792576</v>
+        <v>27.75169581985602</v>
       </c>
       <c r="D18">
-        <v>37.01414633792576</v>
+        <v>36.39069581985602</v>
       </c>
       <c r="E18">
-        <v>-5.643999999999998</v>
+        <v>-5.127999999999998</v>
       </c>
       <c r="F18">
-        <v>8.256</v>
+        <v>8.772</v>
       </c>
       <c r="G18">
         <v>0.133</v>
@@ -3007,37 +3007,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M18">
-        <v>1.9467648</v>
+        <v>2.0684376</v>
       </c>
       <c r="N18">
-        <v>-1.273431466666667</v>
+        <v>-1.395104266666667</v>
       </c>
       <c r="O18">
-        <v>-0.3183578666666667</v>
+        <v>-0.3487760666666667</v>
       </c>
       <c r="P18">
-        <v>-0.9550736</v>
+        <v>-1.0463282</v>
       </c>
       <c r="Q18">
-        <v>0.2049264</v>
+        <v>0.1136717999999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1455201617468404</v>
+        <v>0.14672160947873</v>
       </c>
       <c r="T18">
-        <v>1.943731561485372</v>
+        <v>1.967150014033389</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.0864682437926417</v>
+        <v>0.08138187651072161</v>
       </c>
       <c r="W18">
-        <v>0.2154107881136951</v>
+        <v>0.2166101535187719</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3458729751705668</v>
+        <v>0.3255275060428864</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1586026619655371</v>
+        <v>0.1605026619655371</v>
       </c>
       <c r="C19">
-        <v>27.75169581985602</v>
+        <v>26.63289967831137</v>
       </c>
       <c r="D19">
-        <v>36.39069581985602</v>
+        <v>35.78789967831137</v>
       </c>
       <c r="E19">
-        <v>-5.127999999999998</v>
+        <v>-4.611999999999997</v>
       </c>
       <c r="F19">
-        <v>8.772</v>
+        <v>9.288000000000002</v>
       </c>
       <c r="G19">
         <v>0.133</v>
@@ -3089,37 +3089,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M19">
-        <v>2.0684376</v>
+        <v>2.1901104</v>
       </c>
       <c r="N19">
-        <v>-1.395104266666667</v>
+        <v>-1.516777066666667</v>
       </c>
       <c r="O19">
-        <v>-0.3487760666666667</v>
+        <v>-0.3791942666666667</v>
       </c>
       <c r="P19">
-        <v>-1.0463282</v>
+        <v>-1.1375828</v>
       </c>
       <c r="Q19">
-        <v>0.1136717999999999</v>
+        <v>0.0224171999999998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.14672160947873</v>
+        <v>0.1479523608138365</v>
       </c>
       <c r="T19">
-        <v>1.967150014033389</v>
+        <v>1.991139648350869</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.08138187651072161</v>
+        <v>0.07686066114901484</v>
       </c>
       <c r="W19">
-        <v>0.2166101535187719</v>
+        <v>0.2176762561010623</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3255275060428864</v>
+        <v>0.3074426445960594</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3135,22 +3135,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1605026619655371</v>
+        <v>0.1624026619655372</v>
       </c>
       <c r="C20">
-        <v>26.63289967831137</v>
+        <v>25.53374824555172</v>
       </c>
       <c r="D20">
-        <v>35.78789967831137</v>
+        <v>35.20474824555172</v>
       </c>
       <c r="E20">
-        <v>-4.611999999999998</v>
+        <v>-4.095999999999998</v>
       </c>
       <c r="F20">
-        <v>9.288</v>
+        <v>9.804</v>
       </c>
       <c r="G20">
         <v>0.133</v>
@@ -3171,37 +3171,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M20">
-        <v>2.1901104</v>
+        <v>2.3117832</v>
       </c>
       <c r="N20">
-        <v>-1.516777066666666</v>
+        <v>-1.638449866666667</v>
       </c>
       <c r="O20">
-        <v>-0.3791942666666666</v>
+        <v>-0.4096124666666667</v>
       </c>
       <c r="P20">
-        <v>-1.1375828</v>
+        <v>-1.2288374</v>
       </c>
       <c r="Q20">
-        <v>0.02241720000000003</v>
+        <v>-0.06883740000000005</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1479523608138365</v>
+        <v>0.1492135010707974</v>
       </c>
       <c r="T20">
-        <v>1.991139648350869</v>
+        <v>2.015721619318164</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07686066114901485</v>
+        <v>0.07281536319380354</v>
       </c>
       <c r="W20">
-        <v>0.2176762561010623</v>
+        <v>0.2186301373589011</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3074426445960594</v>
+        <v>0.2912614527752142</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3217,22 +3217,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1624026619655372</v>
+        <v>0.1643026619655372</v>
       </c>
       <c r="C21">
-        <v>25.53374824555172</v>
+        <v>24.45329660744421</v>
       </c>
       <c r="D21">
-        <v>35.20474824555172</v>
+        <v>34.64029660744421</v>
       </c>
       <c r="E21">
-        <v>-4.095999999999998</v>
+        <v>-3.579999999999998</v>
       </c>
       <c r="F21">
-        <v>9.804</v>
+        <v>10.32</v>
       </c>
       <c r="G21">
         <v>0.133</v>
@@ -3253,37 +3253,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M21">
-        <v>2.3117832</v>
+        <v>2.433456</v>
       </c>
       <c r="N21">
-        <v>-1.638449866666667</v>
+        <v>-1.760122666666667</v>
       </c>
       <c r="O21">
-        <v>-0.4096124666666667</v>
+        <v>-0.4400306666666666</v>
       </c>
       <c r="P21">
-        <v>-1.2288374</v>
+        <v>-1.320092</v>
       </c>
       <c r="Q21">
-        <v>-0.06883740000000005</v>
+        <v>-0.1600919999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1492135010707974</v>
+        <v>0.1505061698341824</v>
       </c>
       <c r="T21">
-        <v>2.015721619318164</v>
+        <v>2.040918139559641</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.07281536319380354</v>
+        <v>0.06917459503411337</v>
       </c>
       <c r="W21">
-        <v>0.2186301373589011</v>
+        <v>0.2194886304909561</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2912614527752142</v>
+        <v>0.2766983801364535</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3299,22 +3299,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1643026619655372</v>
+        <v>0.1662026619655372</v>
       </c>
       <c r="C22">
-        <v>24.45329660744421</v>
+        <v>23.39065949427986</v>
       </c>
       <c r="D22">
-        <v>34.64029660744421</v>
+        <v>34.09365949427986</v>
       </c>
       <c r="E22">
-        <v>-3.579999999999998</v>
+        <v>-3.063999999999997</v>
       </c>
       <c r="F22">
-        <v>10.32</v>
+        <v>10.836</v>
       </c>
       <c r="G22">
         <v>0.133</v>
@@ -3335,37 +3335,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M22">
-        <v>2.433456</v>
+        <v>2.555128800000001</v>
       </c>
       <c r="N22">
-        <v>-1.760122666666667</v>
+        <v>-1.881795466666667</v>
       </c>
       <c r="O22">
-        <v>-0.4400306666666666</v>
+        <v>-0.4704488666666668</v>
       </c>
       <c r="P22">
-        <v>-1.320092</v>
+        <v>-1.4113466</v>
       </c>
       <c r="Q22">
-        <v>-0.1600919999999999</v>
+        <v>-0.2513466000000004</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1505061698341824</v>
+        <v>0.1518315643890455</v>
       </c>
       <c r="T22">
-        <v>2.040918139559641</v>
+        <v>2.06675254638951</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06917459503411337</v>
+        <v>0.06588056669915557</v>
       </c>
       <c r="W22">
-        <v>0.2194886304909561</v>
+        <v>0.2202653623723391</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2766983801364535</v>
+        <v>0.2635222667966223</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1662026619655371</v>
+        <v>0.1681026619655371</v>
       </c>
       <c r="C23">
-        <v>23.39065949427987</v>
+        <v>22.34500664782436</v>
       </c>
       <c r="D23">
-        <v>34.09365949427986</v>
+        <v>33.56400664782436</v>
       </c>
       <c r="E23">
-        <v>-3.063999999999998</v>
+        <v>-2.547999999999998</v>
       </c>
       <c r="F23">
-        <v>10.836</v>
+        <v>11.352</v>
       </c>
       <c r="G23">
         <v>0.133</v>
@@ -3417,37 +3417,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M23">
-        <v>2.5551288</v>
+        <v>2.6768016</v>
       </c>
       <c r="N23">
-        <v>-1.881795466666667</v>
+        <v>-2.003468266666666</v>
       </c>
       <c r="O23">
-        <v>-0.4704488666666667</v>
+        <v>-0.5008670666666666</v>
       </c>
       <c r="P23">
-        <v>-1.4113466</v>
+        <v>-1.5026012</v>
       </c>
       <c r="Q23">
-        <v>-0.2513466000000002</v>
+        <v>-0.3426011999999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1518315643890455</v>
+        <v>0.1531909434196743</v>
       </c>
       <c r="T23">
-        <v>2.066752546389509</v>
+        <v>2.093249373907324</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06588056669915558</v>
+        <v>0.06288599548555761</v>
       </c>
       <c r="W23">
-        <v>0.2202653623723391</v>
+        <v>0.2209714822645055</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2635222667966224</v>
+        <v>0.2515439819422305</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3463,22 +3463,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1681026619655371</v>
+        <v>0.1700026619655371</v>
       </c>
       <c r="C24">
-        <v>22.34500664782436</v>
+        <v>21.31555861360621</v>
       </c>
       <c r="D24">
-        <v>33.56400664782436</v>
+        <v>33.05055861360621</v>
       </c>
       <c r="E24">
-        <v>-2.547999999999998</v>
+        <v>-2.031999999999998</v>
       </c>
       <c r="F24">
-        <v>11.352</v>
+        <v>11.868</v>
       </c>
       <c r="G24">
         <v>0.133</v>
@@ -3499,37 +3499,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M24">
-        <v>2.6768016</v>
+        <v>2.7984744</v>
       </c>
       <c r="N24">
-        <v>-2.003468266666666</v>
+        <v>-2.125141066666667</v>
       </c>
       <c r="O24">
-        <v>-0.5008670666666666</v>
+        <v>-0.5312852666666668</v>
       </c>
       <c r="P24">
-        <v>-1.5026012</v>
+        <v>-1.5938558</v>
       </c>
       <c r="Q24">
-        <v>-0.3426011999999998</v>
+        <v>-0.4338558000000003</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1531909434196743</v>
+        <v>0.1545856309965531</v>
       </c>
       <c r="T24">
-        <v>2.093249373907324</v>
+        <v>2.120434430711315</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06288599548555761</v>
+        <v>0.06015182176879423</v>
       </c>
       <c r="W24">
-        <v>0.2209714822645055</v>
+        <v>0.2216162004269183</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2515439819422305</v>
+        <v>0.2406072870751769</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3545,22 +3545,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1700026619655371</v>
+        <v>0.1719026619655371</v>
       </c>
       <c r="C25">
-        <v>21.31555861360621</v>
+        <v>20.30158291359273</v>
       </c>
       <c r="D25">
-        <v>33.05055861360621</v>
+        <v>32.55258291359273</v>
       </c>
       <c r="E25">
-        <v>-2.031999999999998</v>
+        <v>-1.515999999999996</v>
       </c>
       <c r="F25">
-        <v>11.868</v>
+        <v>12.384</v>
       </c>
       <c r="G25">
         <v>0.133</v>
@@ -3581,37 +3581,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M25">
-        <v>2.7984744</v>
+        <v>2.920147200000001</v>
       </c>
       <c r="N25">
-        <v>-2.125141066666667</v>
+        <v>-2.246813866666667</v>
       </c>
       <c r="O25">
-        <v>-0.5312852666666668</v>
+        <v>-0.5617034666666667</v>
       </c>
       <c r="P25">
-        <v>-1.5938558</v>
+        <v>-1.6851104</v>
       </c>
       <c r="Q25">
-        <v>-0.4338558000000003</v>
+        <v>-0.5251104000000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1545856309965531</v>
+        <v>0.1560170208780867</v>
       </c>
       <c r="T25">
-        <v>2.120434430711315</v>
+        <v>2.14833488374699</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.06015182176879423</v>
+        <v>0.05764549586176113</v>
       </c>
       <c r="W25">
-        <v>0.2216162004269183</v>
+        <v>0.2222071920757967</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2406072870751769</v>
+        <v>0.2305819834470446</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3627,22 +3627,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1719026619655371</v>
+        <v>0.1738026619655371</v>
       </c>
       <c r="C26">
-        <v>20.30158291359275</v>
+        <v>19.30239055972999</v>
       </c>
       <c r="D26">
-        <v>32.55258291359274</v>
+        <v>32.06939055972998</v>
       </c>
       <c r="E26">
-        <v>-1.515999999999998</v>
+        <v>-0.9999999999999982</v>
       </c>
       <c r="F26">
-        <v>12.384</v>
+        <v>12.9</v>
       </c>
       <c r="G26">
         <v>0.133</v>
@@ -3663,37 +3663,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M26">
-        <v>2.9201472</v>
+        <v>3.04182</v>
       </c>
       <c r="N26">
-        <v>-2.246813866666667</v>
+        <v>-2.368486666666667</v>
       </c>
       <c r="O26">
-        <v>-0.5617034666666667</v>
+        <v>-0.5921216666666667</v>
       </c>
       <c r="P26">
-        <v>-1.6851104</v>
+        <v>-1.776365</v>
       </c>
       <c r="Q26">
-        <v>-0.5251104000000002</v>
+        <v>-0.6163650000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1560170208780867</v>
+        <v>0.1574865811564612</v>
       </c>
       <c r="T26">
-        <v>2.14833488374699</v>
+        <v>2.176979348863616</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05764549586176114</v>
+        <v>0.05533967602729069</v>
       </c>
       <c r="W26">
-        <v>0.2222071920757967</v>
+        <v>0.2227509043927648</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2305819834470445</v>
+        <v>0.2213587041091628</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3709,22 +3709,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1738026619655371</v>
+        <v>0.1757026619655371</v>
       </c>
       <c r="C27">
-        <v>19.30239055972999</v>
+        <v>18.31733287344752</v>
       </c>
       <c r="D27">
-        <v>32.06939055972998</v>
+        <v>31.60033287344752</v>
       </c>
       <c r="E27">
-        <v>-0.9999999999999982</v>
+        <v>-0.4839999999999982</v>
       </c>
       <c r="F27">
-        <v>12.9</v>
+        <v>13.416</v>
       </c>
       <c r="G27">
         <v>0.133</v>
@@ -3745,37 +3745,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M27">
-        <v>3.04182</v>
+        <v>3.1634928</v>
       </c>
       <c r="N27">
-        <v>-2.368486666666667</v>
+        <v>-2.490159466666666</v>
       </c>
       <c r="O27">
-        <v>-0.5921216666666667</v>
+        <v>-0.6225398666666666</v>
       </c>
       <c r="P27">
-        <v>-1.776365</v>
+        <v>-1.8676196</v>
       </c>
       <c r="Q27">
-        <v>-0.6163650000000001</v>
+        <v>-0.7076195999999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1574865811564612</v>
+        <v>0.1589958592801972</v>
       </c>
       <c r="T27">
-        <v>2.176979348863616</v>
+        <v>2.206397988713126</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05533967602729069</v>
+        <v>0.05321122694931797</v>
       </c>
       <c r="W27">
-        <v>0.2227509043927648</v>
+        <v>0.2232527926853508</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2213587041091628</v>
+        <v>0.2128449077972719</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3791,22 +3791,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1757026619655371</v>
+        <v>0.1776026619655371</v>
       </c>
       <c r="C28">
-        <v>18.31733287344752</v>
+        <v>17.34579858025358</v>
       </c>
       <c r="D28">
-        <v>31.60033287344752</v>
+        <v>31.14479858025358</v>
       </c>
       <c r="E28">
-        <v>-0.4839999999999982</v>
+        <v>0.03200000000000358</v>
       </c>
       <c r="F28">
-        <v>13.416</v>
+        <v>13.932</v>
       </c>
       <c r="G28">
         <v>0.133</v>
@@ -3827,37 +3827,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M28">
-        <v>3.1634928</v>
+        <v>3.2851656</v>
       </c>
       <c r="N28">
-        <v>-2.490159466666666</v>
+        <v>-2.611832266666667</v>
       </c>
       <c r="O28">
-        <v>-0.6225398666666666</v>
+        <v>-0.6529580666666668</v>
       </c>
       <c r="P28">
-        <v>-1.8676196</v>
+        <v>-1.9588742</v>
       </c>
       <c r="Q28">
-        <v>-0.7076195999999999</v>
+        <v>-0.7988742000000004</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1589958592801972</v>
+        <v>0.160546487489515</v>
       </c>
       <c r="T28">
-        <v>2.206397988713126</v>
+        <v>2.236622618695497</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05321122694931797</v>
+        <v>0.0512404407660099</v>
       </c>
       <c r="W28">
-        <v>0.2232527926853508</v>
+        <v>0.2237175040673749</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2128449077972719</v>
+        <v>0.2049617630640396</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3873,22 +3873,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1776026619655371</v>
+        <v>0.1795026619655372</v>
       </c>
       <c r="C29">
-        <v>17.34579858025358</v>
+        <v>16.38721115205611</v>
       </c>
       <c r="D29">
-        <v>31.14479858025358</v>
+        <v>30.70221115205612</v>
       </c>
       <c r="E29">
-        <v>0.03200000000000358</v>
+        <v>0.5480000000000036</v>
       </c>
       <c r="F29">
-        <v>13.932</v>
+        <v>14.448</v>
       </c>
       <c r="G29">
         <v>0.133</v>
@@ -3909,37 +3909,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M29">
-        <v>3.2851656</v>
+        <v>3.406838400000001</v>
       </c>
       <c r="N29">
-        <v>-2.611832266666667</v>
+        <v>-2.733505066666667</v>
       </c>
       <c r="O29">
-        <v>-0.6529580666666668</v>
+        <v>-0.6833762666666667</v>
       </c>
       <c r="P29">
-        <v>-1.9588742</v>
+        <v>-2.0501288</v>
       </c>
       <c r="Q29">
-        <v>-0.7988742000000004</v>
+        <v>-0.8901288000000005</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.160546487489515</v>
+        <v>0.1621401887046471</v>
       </c>
       <c r="T29">
-        <v>2.236622618695497</v>
+        <v>2.267686821732934</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.0512404407660099</v>
+        <v>0.04941042502436668</v>
       </c>
       <c r="W29">
-        <v>0.2237175040673749</v>
+        <v>0.2241490217792544</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2049617630640396</v>
+        <v>0.1976417000974668</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3955,22 +3955,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1795026619655372</v>
+        <v>0.1814026619655372</v>
       </c>
       <c r="C30">
-        <v>16.38721115205611</v>
+        <v>15.44102637291267</v>
       </c>
       <c r="D30">
-        <v>30.70221115205612</v>
+        <v>30.27202637291267</v>
       </c>
       <c r="E30">
-        <v>0.5480000000000036</v>
+        <v>1.064000000000004</v>
       </c>
       <c r="F30">
-        <v>14.448</v>
+        <v>14.964</v>
       </c>
       <c r="G30">
         <v>0.133</v>
@@ -3991,37 +3991,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M30">
-        <v>3.406838400000001</v>
+        <v>3.528511200000001</v>
       </c>
       <c r="N30">
-        <v>-2.733505066666667</v>
+        <v>-2.855177866666667</v>
       </c>
       <c r="O30">
-        <v>-0.6833762666666667</v>
+        <v>-0.7137944666666667</v>
       </c>
       <c r="P30">
-        <v>-2.0501288</v>
+        <v>-2.1413834</v>
       </c>
       <c r="Q30">
-        <v>-0.8901288000000005</v>
+        <v>-0.9813834000000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1621401887046471</v>
+        <v>0.1637787829117548</v>
       </c>
       <c r="T30">
-        <v>2.267686821732934</v>
+        <v>2.299626072743258</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04941042502436668</v>
+        <v>0.04770661726490576</v>
       </c>
       <c r="W30">
-        <v>0.2241490217792544</v>
+        <v>0.2245507796489352</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1976417000974668</v>
+        <v>0.1908264690596231</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4037,22 +4037,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1814026619655371</v>
+        <v>0.1833026619655371</v>
       </c>
       <c r="C31">
-        <v>15.44102637291268</v>
+        <v>14.50673010659786</v>
       </c>
       <c r="D31">
-        <v>30.27202637291268</v>
+        <v>29.85373010659786</v>
       </c>
       <c r="E31">
-        <v>1.064</v>
+        <v>1.580000000000002</v>
       </c>
       <c r="F31">
-        <v>14.964</v>
+        <v>15.48</v>
       </c>
       <c r="G31">
         <v>0.133</v>
@@ -4073,37 +4073,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M31">
-        <v>3.5285112</v>
+        <v>3.650184</v>
       </c>
       <c r="N31">
-        <v>-2.855177866666666</v>
+        <v>-2.976850666666667</v>
       </c>
       <c r="O31">
-        <v>-0.7137944666666665</v>
+        <v>-0.7442126666666666</v>
       </c>
       <c r="P31">
-        <v>-2.1413834</v>
+        <v>-2.232638</v>
       </c>
       <c r="Q31">
-        <v>-0.9813833999999997</v>
+        <v>-1.072638</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1637787829117548</v>
+        <v>0.1654641940962085</v>
       </c>
       <c r="T31">
-        <v>2.299626072743258</v>
+        <v>2.332477873782447</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04770661726490578</v>
+        <v>0.04611639668940891</v>
       </c>
       <c r="W31">
-        <v>0.2245507796489352</v>
+        <v>0.2249257536606374</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1908264690596232</v>
+        <v>0.1844655867576357</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1833026619655371</v>
+        <v>0.1852026619655371</v>
       </c>
       <c r="C32">
-        <v>14.50673010659786</v>
+        <v>13.58383624673341</v>
       </c>
       <c r="D32">
-        <v>29.85373010659786</v>
+        <v>29.44683624673341</v>
       </c>
       <c r="E32">
-        <v>1.580000000000002</v>
+        <v>2.096000000000002</v>
       </c>
       <c r="F32">
-        <v>15.48</v>
+        <v>15.996</v>
       </c>
       <c r="G32">
         <v>0.133</v>
@@ -4155,37 +4155,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M32">
-        <v>3.650184</v>
+        <v>3.7718568</v>
       </c>
       <c r="N32">
-        <v>-2.976850666666667</v>
+        <v>-3.098523466666666</v>
       </c>
       <c r="O32">
-        <v>-0.7442126666666666</v>
+        <v>-0.7746308666666666</v>
       </c>
       <c r="P32">
-        <v>-2.232638</v>
+        <v>-2.3238926</v>
       </c>
       <c r="Q32">
-        <v>-1.072638</v>
+        <v>-1.1638926</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1654641940962085</v>
+        <v>0.1671984577787622</v>
       </c>
       <c r="T32">
-        <v>2.332477873782447</v>
+        <v>2.366281900938714</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04611639668940891</v>
+        <v>0.04462877098975056</v>
       </c>
       <c r="W32">
-        <v>0.2249257536606374</v>
+        <v>0.2252765358006168</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1844655867576357</v>
+        <v>0.1785150839590023</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4201,22 +4201,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1852026619655371</v>
+        <v>0.1871026619655371</v>
       </c>
       <c r="C33">
-        <v>13.58383624673341</v>
+        <v>12.67188483229765</v>
       </c>
       <c r="D33">
-        <v>29.44683624673341</v>
+        <v>29.05088483229765</v>
       </c>
       <c r="E33">
-        <v>2.096000000000002</v>
+        <v>2.612000000000002</v>
       </c>
       <c r="F33">
-        <v>15.996</v>
+        <v>16.512</v>
       </c>
       <c r="G33">
         <v>0.133</v>
@@ -4237,37 +4237,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M33">
-        <v>3.7718568</v>
+        <v>3.8935296</v>
       </c>
       <c r="N33">
-        <v>-3.098523466666666</v>
+        <v>-3.220196266666667</v>
       </c>
       <c r="O33">
-        <v>-0.7746308666666666</v>
+        <v>-0.8050490666666668</v>
       </c>
       <c r="P33">
-        <v>-2.3238926</v>
+        <v>-2.4151472</v>
       </c>
       <c r="Q33">
-        <v>-1.1638926</v>
+        <v>-1.2551472</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1671984577787622</v>
+        <v>0.1689837292166852</v>
       </c>
       <c r="T33">
-        <v>2.366281900938714</v>
+        <v>2.401080164187813</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04462877098975056</v>
+        <v>0.04323412189632085</v>
       </c>
       <c r="W33">
-        <v>0.2252765358006168</v>
+        <v>0.2256053940568476</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1785150839590023</v>
+        <v>0.1729364875852833</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4283,22 +4283,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1871026619655371</v>
+        <v>0.1890026619655371</v>
       </c>
       <c r="C34">
-        <v>12.67188483229765</v>
+        <v>11.77044031315421</v>
       </c>
       <c r="D34">
-        <v>29.05088483229765</v>
+        <v>28.66544031315421</v>
       </c>
       <c r="E34">
-        <v>2.612000000000002</v>
+        <v>3.128000000000004</v>
       </c>
       <c r="F34">
-        <v>16.512</v>
+        <v>17.028</v>
       </c>
       <c r="G34">
         <v>0.133</v>
@@ -4319,37 +4319,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M34">
-        <v>3.8935296</v>
+        <v>4.015202400000001</v>
       </c>
       <c r="N34">
-        <v>-3.220196266666667</v>
+        <v>-3.341869066666667</v>
       </c>
       <c r="O34">
-        <v>-0.8050490666666668</v>
+        <v>-0.8354672666666667</v>
       </c>
       <c r="P34">
-        <v>-2.4151472</v>
+        <v>-2.5064018</v>
       </c>
       <c r="Q34">
-        <v>-1.2551472</v>
+        <v>-1.3464018</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1689837292166852</v>
+        <v>0.1708222923393223</v>
       </c>
       <c r="T34">
-        <v>2.401080164187813</v>
+        <v>2.43691718156375</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04323412189632085</v>
+        <v>0.04192399699037173</v>
       </c>
       <c r="W34">
-        <v>0.2256053940568476</v>
+        <v>0.2259143215096704</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1729364875852833</v>
+        <v>0.167695987961487</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4365,22 +4365,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1890026619655371</v>
+        <v>0.1909026619655371</v>
       </c>
       <c r="C35">
-        <v>11.77044031315421</v>
+        <v>10.87908995184983</v>
       </c>
       <c r="D35">
-        <v>28.66544031315421</v>
+        <v>28.29008995184983</v>
       </c>
       <c r="E35">
-        <v>3.128000000000004</v>
+        <v>3.644000000000002</v>
       </c>
       <c r="F35">
-        <v>17.028</v>
+        <v>17.544</v>
       </c>
       <c r="G35">
         <v>0.133</v>
@@ -4401,37 +4401,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M35">
-        <v>4.015202400000001</v>
+        <v>4.1368752</v>
       </c>
       <c r="N35">
-        <v>-3.341869066666667</v>
+        <v>-3.463541866666667</v>
       </c>
       <c r="O35">
-        <v>-0.8354672666666667</v>
+        <v>-0.8658854666666667</v>
       </c>
       <c r="P35">
-        <v>-2.5064018</v>
+        <v>-2.5976564</v>
       </c>
       <c r="Q35">
-        <v>-1.3464018</v>
+        <v>-1.4376564</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1708222923393223</v>
+        <v>0.1727165694959787</v>
       </c>
       <c r="T35">
-        <v>2.43691718156375</v>
+        <v>2.473840169163201</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04192399699037173</v>
+        <v>0.0406909382553608</v>
       </c>
       <c r="W35">
-        <v>0.2259143215096704</v>
+        <v>0.2262050767593859</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.167695987961487</v>
+        <v>0.1627637530214433</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1909026619655371</v>
+        <v>0.1928026619655371</v>
       </c>
       <c r="C36">
-        <v>10.87908995184983</v>
+        <v>9.997442349351878</v>
       </c>
       <c r="D36">
-        <v>28.29008995184983</v>
+        <v>27.92444234935188</v>
       </c>
       <c r="E36">
-        <v>3.644000000000002</v>
+        <v>4.160000000000004</v>
       </c>
       <c r="F36">
-        <v>17.544</v>
+        <v>18.06</v>
       </c>
       <c r="G36">
         <v>0.133</v>
@@ -4483,37 +4483,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M36">
-        <v>4.1368752</v>
+        <v>4.258548000000001</v>
       </c>
       <c r="N36">
-        <v>-3.463541866666667</v>
+        <v>-3.585214666666667</v>
       </c>
       <c r="O36">
-        <v>-0.8658854666666667</v>
+        <v>-0.8963036666666668</v>
       </c>
       <c r="P36">
-        <v>-2.5976564</v>
+        <v>-2.688911</v>
       </c>
       <c r="Q36">
-        <v>-1.4376564</v>
+        <v>-1.528911000000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1727165694959787</v>
+        <v>0.1746691321036091</v>
       </c>
       <c r="T36">
-        <v>2.473840169163201</v>
+        <v>2.511899248688789</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0406909382553608</v>
+        <v>0.03952834001949335</v>
       </c>
       <c r="W36">
-        <v>0.2262050767593859</v>
+        <v>0.2264792174234035</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1627637530214433</v>
+        <v>0.1581133600779734</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4529,22 +4529,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1928026619655371</v>
+        <v>0.1947026619655371</v>
       </c>
       <c r="C37">
-        <v>9.997442349351878</v>
+        <v>9.125126083655772</v>
       </c>
       <c r="D37">
-        <v>27.92444234935188</v>
+        <v>27.56812608365578</v>
       </c>
       <c r="E37">
-        <v>4.160000000000004</v>
+        <v>4.676000000000005</v>
       </c>
       <c r="F37">
-        <v>18.06</v>
+        <v>18.576</v>
       </c>
       <c r="G37">
         <v>0.133</v>
@@ -4565,37 +4565,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M37">
-        <v>4.258548000000001</v>
+        <v>4.380220800000001</v>
       </c>
       <c r="N37">
-        <v>-3.585214666666667</v>
+        <v>-3.706887466666667</v>
       </c>
       <c r="O37">
-        <v>-0.8963036666666668</v>
+        <v>-0.9267218666666668</v>
       </c>
       <c r="P37">
-        <v>-2.688911</v>
+        <v>-2.7801656</v>
       </c>
       <c r="Q37">
-        <v>-1.528911000000001</v>
+        <v>-1.6201656</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1746691321036091</v>
+        <v>0.176682712292728</v>
       </c>
       <c r="T37">
-        <v>2.511899248688789</v>
+        <v>2.551147674449551</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03952834001949335</v>
+        <v>0.03843033057450742</v>
       </c>
       <c r="W37">
-        <v>0.2264792174234035</v>
+        <v>0.2267381280505312</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1581133600779734</v>
+        <v>0.1537213222980297</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4611,22 +4611,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1947026619655371</v>
+        <v>0.1966026619655372</v>
       </c>
       <c r="C38">
-        <v>9.125126083655775</v>
+        <v>8.261788451307375</v>
       </c>
       <c r="D38">
-        <v>27.56812608365578</v>
+        <v>27.22078845130737</v>
       </c>
       <c r="E38">
-        <v>4.676000000000002</v>
+        <v>5.192</v>
       </c>
       <c r="F38">
-        <v>18.576</v>
+        <v>19.092</v>
       </c>
       <c r="G38">
         <v>0.133</v>
@@ -4647,37 +4647,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M38">
-        <v>4.3802208</v>
+        <v>4.5018936</v>
       </c>
       <c r="N38">
-        <v>-3.706887466666666</v>
+        <v>-3.828560266666666</v>
       </c>
       <c r="O38">
-        <v>-0.9267218666666666</v>
+        <v>-0.9571400666666665</v>
       </c>
       <c r="P38">
-        <v>-2.7801656</v>
+        <v>-2.871420199999999</v>
       </c>
       <c r="Q38">
-        <v>-1.6201656</v>
+        <v>-1.711420199999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.176682712292728</v>
+        <v>0.1787602156624539</v>
       </c>
       <c r="T38">
-        <v>2.551147674449551</v>
+        <v>2.591642081980496</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03843033057450743</v>
+        <v>0.03739167299141263</v>
       </c>
       <c r="W38">
-        <v>0.2267381280505312</v>
+        <v>0.2269830435086249</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1537213222980298</v>
+        <v>0.1495666919656506</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1966026619655372</v>
+        <v>0.1985026619655371</v>
       </c>
       <c r="C39">
-        <v>8.261788451307375</v>
+        <v>7.407094302876914</v>
       </c>
       <c r="D39">
-        <v>27.22078845130737</v>
+        <v>26.88209430287692</v>
       </c>
       <c r="E39">
-        <v>5.192</v>
+        <v>5.708000000000002</v>
       </c>
       <c r="F39">
-        <v>19.092</v>
+        <v>19.608</v>
       </c>
       <c r="G39">
         <v>0.133</v>
@@ -4729,37 +4729,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M39">
-        <v>4.5018936</v>
+        <v>4.623566400000001</v>
       </c>
       <c r="N39">
-        <v>-3.828560266666666</v>
+        <v>-3.950233066666667</v>
       </c>
       <c r="O39">
-        <v>-0.9571400666666665</v>
+        <v>-0.9875582666666667</v>
       </c>
       <c r="P39">
-        <v>-2.871420199999999</v>
+        <v>-2.9626748</v>
       </c>
       <c r="Q39">
-        <v>-1.711420199999999</v>
+        <v>-1.8026748</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1787602156624539</v>
+        <v>0.1809047352699128</v>
       </c>
       <c r="T39">
-        <v>2.591642081980496</v>
+        <v>2.633442760722117</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03739167299141263</v>
+        <v>0.03640768159690177</v>
       </c>
       <c r="W39">
-        <v>0.2269830435086249</v>
+        <v>0.2272150686794506</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1495666919656506</v>
+        <v>0.1456307263876071</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4775,22 +4775,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1985026619655371</v>
+        <v>0.2004026619655371</v>
       </c>
       <c r="C40">
-        <v>7.407094302876914</v>
+        <v>6.560724964302047</v>
       </c>
       <c r="D40">
-        <v>26.88209430287692</v>
+        <v>26.55172496430205</v>
       </c>
       <c r="E40">
-        <v>5.708000000000002</v>
+        <v>6.224000000000004</v>
       </c>
       <c r="F40">
-        <v>19.608</v>
+        <v>20.124</v>
       </c>
       <c r="G40">
         <v>0.133</v>
@@ -4811,37 +4811,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M40">
-        <v>4.623566400000001</v>
+        <v>4.7452392</v>
       </c>
       <c r="N40">
-        <v>-3.950233066666667</v>
+        <v>-4.071905866666667</v>
       </c>
       <c r="O40">
-        <v>-0.9875582666666667</v>
+        <v>-1.017976466666667</v>
       </c>
       <c r="P40">
-        <v>-2.9626748</v>
+        <v>-3.0539294</v>
       </c>
       <c r="Q40">
-        <v>-1.8026748</v>
+        <v>-1.8939294</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1809047352699128</v>
+        <v>0.1831195669956491</v>
       </c>
       <c r="T40">
-        <v>2.633442760722117</v>
+        <v>2.676613953520841</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03640768159690177</v>
+        <v>0.03547415129954531</v>
       </c>
       <c r="W40">
-        <v>0.2272150686794506</v>
+        <v>0.2274351951235672</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1456307263876071</v>
+        <v>0.1418966051981813</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4857,22 +4857,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2004026619655371</v>
+        <v>0.2023026619655371</v>
       </c>
       <c r="C41">
-        <v>6.560724964302047</v>
+        <v>5.722377236802807</v>
       </c>
       <c r="D41">
-        <v>26.55172496430205</v>
+        <v>26.22937723680281</v>
       </c>
       <c r="E41">
-        <v>6.224000000000004</v>
+        <v>6.740000000000002</v>
       </c>
       <c r="F41">
-        <v>20.124</v>
+        <v>20.64</v>
       </c>
       <c r="G41">
         <v>0.133</v>
@@ -4893,37 +4893,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M41">
-        <v>4.7452392</v>
+        <v>4.866912</v>
       </c>
       <c r="N41">
-        <v>-4.071905866666667</v>
+        <v>-4.193578666666666</v>
       </c>
       <c r="O41">
-        <v>-1.017976466666667</v>
+        <v>-1.048394666666667</v>
       </c>
       <c r="P41">
-        <v>-3.0539294</v>
+        <v>-3.145184</v>
       </c>
       <c r="Q41">
-        <v>-1.8939294</v>
+        <v>-1.985184</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1831195669956491</v>
+        <v>0.1854082264455765</v>
       </c>
       <c r="T41">
-        <v>2.676613953520841</v>
+        <v>2.721224186079521</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03547415129954531</v>
+        <v>0.03458729751705669</v>
       </c>
       <c r="W41">
-        <v>0.2274351951235672</v>
+        <v>0.227644315245478</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1418966051981813</v>
+        <v>0.1383491900682268</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4939,22 +4939,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2023026619655371</v>
+        <v>0.2042026619655372</v>
       </c>
       <c r="C42">
-        <v>5.722377236802807</v>
+        <v>4.891762468770885</v>
       </c>
       <c r="D42">
-        <v>26.22937723680281</v>
+        <v>25.91476246877089</v>
       </c>
       <c r="E42">
-        <v>6.740000000000002</v>
+        <v>7.256000000000004</v>
       </c>
       <c r="F42">
-        <v>20.64</v>
+        <v>21.156</v>
       </c>
       <c r="G42">
         <v>0.133</v>
@@ -4975,37 +4975,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M42">
-        <v>4.866912</v>
+        <v>4.988584800000001</v>
       </c>
       <c r="N42">
-        <v>-4.193578666666666</v>
+        <v>-4.315251466666667</v>
       </c>
       <c r="O42">
-        <v>-1.048394666666667</v>
+        <v>-1.078812866666667</v>
       </c>
       <c r="P42">
-        <v>-3.145184</v>
+        <v>-3.2364386</v>
       </c>
       <c r="Q42">
-        <v>-1.985184</v>
+        <v>-2.0764386</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1854082264455765</v>
+        <v>0.1877744675717728</v>
       </c>
       <c r="T42">
-        <v>2.721224186079521</v>
+        <v>2.767346629911378</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03458729751705669</v>
+        <v>0.03374370489468945</v>
       </c>
       <c r="W42">
-        <v>0.227644315245478</v>
+        <v>0.2278432343858322</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1383491900682268</v>
+        <v>0.1349748195787578</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5021,22 +5021,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2042026619655372</v>
+        <v>0.2061026619655372</v>
       </c>
       <c r="C43">
-        <v>4.891762468770885</v>
+        <v>4.068605693662242</v>
       </c>
       <c r="D43">
-        <v>25.91476246877089</v>
+        <v>25.60760569366225</v>
       </c>
       <c r="E43">
-        <v>7.256000000000004</v>
+        <v>7.772000000000006</v>
       </c>
       <c r="F43">
-        <v>21.156</v>
+        <v>21.672</v>
       </c>
       <c r="G43">
         <v>0.133</v>
@@ -5057,37 +5057,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M43">
-        <v>4.988584800000001</v>
+        <v>5.110257600000002</v>
       </c>
       <c r="N43">
-        <v>-4.315251466666667</v>
+        <v>-4.436924266666668</v>
       </c>
       <c r="O43">
-        <v>-1.078812866666667</v>
+        <v>-1.109231066666667</v>
       </c>
       <c r="P43">
-        <v>-3.2364386</v>
+        <v>-3.327693200000001</v>
       </c>
       <c r="Q43">
-        <v>-2.0764386</v>
+        <v>-2.1676932</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1877744675717728</v>
+        <v>0.190222303219562</v>
       </c>
       <c r="T43">
-        <v>2.767346629911378</v>
+        <v>2.815059502840884</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03374370489468945</v>
+        <v>0.03294028334957778</v>
       </c>
       <c r="W43">
-        <v>0.2278432343858322</v>
+        <v>0.2280326811861696</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1349748195787578</v>
+        <v>0.1317611333983112</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5103,22 +5103,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2061026619655371</v>
+        <v>0.2080026619655372</v>
       </c>
       <c r="C44">
-        <v>4.068605693662249</v>
+        <v>3.252644828480541</v>
       </c>
       <c r="D44">
-        <v>25.60760569366225</v>
+        <v>25.30764482848054</v>
       </c>
       <c r="E44">
-        <v>7.772000000000002</v>
+        <v>8.288</v>
       </c>
       <c r="F44">
-        <v>21.672</v>
+        <v>22.188</v>
       </c>
       <c r="G44">
         <v>0.133</v>
@@ -5139,37 +5139,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M44">
-        <v>5.110257600000001</v>
+        <v>5.2319304</v>
       </c>
       <c r="N44">
-        <v>-4.436924266666667</v>
+        <v>-4.558597066666666</v>
       </c>
       <c r="O44">
-        <v>-1.109231066666667</v>
+        <v>-1.139649266666666</v>
       </c>
       <c r="P44">
-        <v>-3.3276932</v>
+        <v>-3.418947799999999</v>
       </c>
       <c r="Q44">
-        <v>-2.1676932</v>
+        <v>-2.2589478</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1902223032195619</v>
+        <v>0.192756027837449</v>
       </c>
       <c r="T44">
-        <v>2.815059502840884</v>
+        <v>2.864446511662654</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03294028334957779</v>
+        <v>0.03217423024842483</v>
       </c>
       <c r="W44">
-        <v>0.2280326811861696</v>
+        <v>0.2282133165074214</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1317611333983112</v>
+        <v>0.1286969209936993</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5185,22 +5185,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2080026619655372</v>
+        <v>0.2099026619655371</v>
       </c>
       <c r="C45">
-        <v>3.252644828480541</v>
+        <v>2.443629927940957</v>
       </c>
       <c r="D45">
-        <v>25.30764482848054</v>
+        <v>25.01462992794096</v>
       </c>
       <c r="E45">
-        <v>8.288</v>
+        <v>8.804000000000002</v>
       </c>
       <c r="F45">
-        <v>22.188</v>
+        <v>22.704</v>
       </c>
       <c r="G45">
         <v>0.133</v>
@@ -5221,37 +5221,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M45">
-        <v>5.2319304</v>
+        <v>5.3536032</v>
       </c>
       <c r="N45">
-        <v>-4.558597066666666</v>
+        <v>-4.680269866666666</v>
       </c>
       <c r="O45">
-        <v>-1.139649266666666</v>
+        <v>-1.170067466666667</v>
       </c>
       <c r="P45">
-        <v>-3.418947799999999</v>
+        <v>-3.5102024</v>
       </c>
       <c r="Q45">
-        <v>-2.2589478</v>
+        <v>-2.3502024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.192756027837449</v>
+        <v>0.1953802426202606</v>
       </c>
       <c r="T45">
-        <v>2.864446511662654</v>
+        <v>2.915597342228058</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03217423024842483</v>
+        <v>0.0314429977427788</v>
       </c>
       <c r="W45">
-        <v>0.2282133165074214</v>
+        <v>0.2283857411322528</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1286969209936993</v>
+        <v>0.1257719909711152</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5267,22 +5267,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2099026619655371</v>
+        <v>0.2118026619655372</v>
       </c>
       <c r="C46">
-        <v>2.443629927940957</v>
+        <v>1.641322489853273</v>
       </c>
       <c r="D46">
-        <v>25.01462992794096</v>
+        <v>24.72832248985328</v>
       </c>
       <c r="E46">
-        <v>8.804000000000002</v>
+        <v>9.320000000000004</v>
       </c>
       <c r="F46">
-        <v>22.704</v>
+        <v>23.22</v>
       </c>
       <c r="G46">
         <v>0.133</v>
@@ -5303,37 +5303,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M46">
-        <v>5.3536032</v>
+        <v>5.475276000000001</v>
       </c>
       <c r="N46">
-        <v>-4.680269866666666</v>
+        <v>-4.801942666666667</v>
       </c>
       <c r="O46">
-        <v>-1.170067466666667</v>
+        <v>-1.200485666666667</v>
       </c>
       <c r="P46">
-        <v>-3.5102024</v>
+        <v>-3.601457</v>
       </c>
       <c r="Q46">
-        <v>-2.3502024</v>
+        <v>-2.441457000000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1953802426202606</v>
+        <v>0.1980998833951744</v>
       </c>
       <c r="T46">
-        <v>2.915597342228058</v>
+        <v>2.968608202995841</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0314429977427788</v>
+        <v>0.03074426445960594</v>
       </c>
       <c r="W46">
-        <v>0.2283857411322528</v>
+        <v>0.2285505024404249</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1257719909711152</v>
+        <v>0.1229770578384238</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2118026619655372</v>
+        <v>0.2137026619655371</v>
       </c>
       <c r="C47">
-        <v>1.641322489853273</v>
+        <v>0.8454948076670128</v>
       </c>
       <c r="D47">
-        <v>24.72832248985328</v>
+        <v>24.44849480766701</v>
       </c>
       <c r="E47">
-        <v>9.320000000000004</v>
+        <v>9.836000000000002</v>
       </c>
       <c r="F47">
-        <v>23.22</v>
+        <v>23.736</v>
       </c>
       <c r="G47">
         <v>0.133</v>
@@ -5385,37 +5385,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M47">
-        <v>5.475276000000001</v>
+        <v>5.596948800000001</v>
       </c>
       <c r="N47">
-        <v>-4.801942666666667</v>
+        <v>-4.923615466666667</v>
       </c>
       <c r="O47">
-        <v>-1.200485666666667</v>
+        <v>-1.230903866666667</v>
       </c>
       <c r="P47">
-        <v>-3.601457</v>
+        <v>-3.6927116</v>
       </c>
       <c r="Q47">
-        <v>-2.441457000000001</v>
+        <v>-2.5327116</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1980998833951744</v>
+        <v>0.2009202516061961</v>
       </c>
       <c r="T47">
-        <v>2.968608202995841</v>
+        <v>3.023582428977245</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03074426445960594</v>
+        <v>0.03007591088439712</v>
       </c>
       <c r="W47">
-        <v>0.2285505024404249</v>
+        <v>0.2287081002134592</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1229770578384238</v>
+        <v>0.1203036435375885</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5431,22 +5431,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2137026619655371</v>
+        <v>0.2156026619655372</v>
       </c>
       <c r="C48">
-        <v>0.8454948076670128</v>
+        <v>0.05592936648449154</v>
       </c>
       <c r="D48">
-        <v>24.44849480766701</v>
+        <v>24.17492936648449</v>
       </c>
       <c r="E48">
-        <v>9.836000000000002</v>
+        <v>10.352</v>
       </c>
       <c r="F48">
-        <v>23.736</v>
+        <v>24.252</v>
       </c>
       <c r="G48">
         <v>0.133</v>
@@ -5467,37 +5467,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M48">
-        <v>5.596948800000001</v>
+        <v>5.718621600000001</v>
       </c>
       <c r="N48">
-        <v>-4.923615466666667</v>
+        <v>-5.045288266666667</v>
       </c>
       <c r="O48">
-        <v>-1.230903866666667</v>
+        <v>-1.261322066666667</v>
       </c>
       <c r="P48">
-        <v>-3.6927116</v>
+        <v>-3.7839662</v>
       </c>
       <c r="Q48">
-        <v>-2.5327116</v>
+        <v>-2.6239662</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2009202516061961</v>
+        <v>0.2038470488063131</v>
       </c>
       <c r="T48">
-        <v>3.023582428977245</v>
+        <v>3.080631154052288</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03007591088439712</v>
+        <v>0.02943599788685675</v>
       </c>
       <c r="W48">
-        <v>0.2287081002134592</v>
+        <v>0.2288589916982792</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1203036435375885</v>
+        <v>0.1177439915474271</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2156026619655372</v>
+        <v>0.2175026619655372</v>
       </c>
       <c r="C49">
-        <v>0.05592936648449154</v>
+        <v>-0.7275817208249222</v>
       </c>
       <c r="D49">
-        <v>24.17492936648449</v>
+        <v>23.90741827917508</v>
       </c>
       <c r="E49">
-        <v>10.352</v>
+        <v>10.86800000000001</v>
       </c>
       <c r="F49">
-        <v>24.252</v>
+        <v>24.768</v>
       </c>
       <c r="G49">
         <v>0.133</v>
@@ -5549,37 +5549,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M49">
-        <v>5.718621600000001</v>
+        <v>5.840294400000001</v>
       </c>
       <c r="N49">
-        <v>-5.045288266666667</v>
+        <v>-5.166961066666667</v>
       </c>
       <c r="O49">
-        <v>-1.261322066666667</v>
+        <v>-1.291740266666667</v>
       </c>
       <c r="P49">
-        <v>-3.7839662</v>
+        <v>-3.875220800000001</v>
       </c>
       <c r="Q49">
-        <v>-2.6239662</v>
+        <v>-2.715220800000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2038470488063131</v>
+        <v>0.2068864151295114</v>
       </c>
       <c r="T49">
-        <v>3.080631154052288</v>
+        <v>3.139874060860986</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02943599788685675</v>
+        <v>0.02882274793088057</v>
       </c>
       <c r="W49">
-        <v>0.2288589916982792</v>
+        <v>0.2290035960378984</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1177439915474271</v>
+        <v>0.1152909917235223</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5595,22 +5595,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2175026619655371</v>
+        <v>0.2194026619655371</v>
       </c>
       <c r="C50">
-        <v>-0.7275817208249116</v>
+        <v>-1.505237240481918</v>
       </c>
       <c r="D50">
-        <v>23.90741827917509</v>
+        <v>23.64576275951808</v>
       </c>
       <c r="E50">
-        <v>10.868</v>
+        <v>11.384</v>
       </c>
       <c r="F50">
-        <v>24.768</v>
+        <v>25.284</v>
       </c>
       <c r="G50">
         <v>0.133</v>
@@ -5631,37 +5631,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M50">
-        <v>5.8402944</v>
+        <v>5.9619672</v>
       </c>
       <c r="N50">
-        <v>-5.166961066666667</v>
+        <v>-5.288633866666666</v>
       </c>
       <c r="O50">
-        <v>-1.291740266666667</v>
+        <v>-1.322158466666667</v>
       </c>
       <c r="P50">
-        <v>-3.8752208</v>
+        <v>-3.9664754</v>
       </c>
       <c r="Q50">
-        <v>-2.7152208</v>
+        <v>-2.8064754</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2068864151295114</v>
+        <v>0.2100449722889136</v>
       </c>
       <c r="T50">
-        <v>3.139874060860986</v>
+        <v>3.201440218917084</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02882274793088057</v>
+        <v>0.0282345285853524</v>
       </c>
       <c r="W50">
-        <v>0.2290035960378984</v>
+        <v>0.2291422981595739</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1152909917235223</v>
+        <v>0.1129381143414097</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5677,22 +5677,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2194026619655371</v>
+        <v>0.2213026619655372</v>
       </c>
       <c r="C51">
-        <v>-1.505237240481918</v>
+        <v>-2.277227370431671</v>
       </c>
       <c r="D51">
-        <v>23.64576275951808</v>
+        <v>23.38977262956833</v>
       </c>
       <c r="E51">
-        <v>11.384</v>
+        <v>11.9</v>
       </c>
       <c r="F51">
-        <v>25.284</v>
+        <v>25.8</v>
       </c>
       <c r="G51">
         <v>0.133</v>
@@ -5713,37 +5713,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M51">
-        <v>5.9619672</v>
+        <v>6.083640000000001</v>
       </c>
       <c r="N51">
-        <v>-5.288633866666666</v>
+        <v>-5.410306666666667</v>
       </c>
       <c r="O51">
-        <v>-1.322158466666667</v>
+        <v>-1.352576666666667</v>
       </c>
       <c r="P51">
-        <v>-3.9664754</v>
+        <v>-4.05773</v>
       </c>
       <c r="Q51">
-        <v>-2.8064754</v>
+        <v>-2.89773</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2100449722889136</v>
+        <v>0.2133298717346918</v>
       </c>
       <c r="T51">
-        <v>3.201440218917084</v>
+        <v>3.265469023295425</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0282345285853524</v>
+        <v>0.02766983801364534</v>
       </c>
       <c r="W51">
-        <v>0.2291422981595739</v>
+        <v>0.2292754521963825</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1129381143414097</v>
+        <v>0.1106793520545815</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5759,22 +5759,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2213026619655372</v>
+        <v>0.2232026619655371</v>
       </c>
       <c r="C52">
-        <v>-2.277227370431671</v>
+        <v>-3.043734141321121</v>
       </c>
       <c r="D52">
-        <v>23.38977262956833</v>
+        <v>23.13926585867888</v>
       </c>
       <c r="E52">
-        <v>11.9</v>
+        <v>12.416</v>
       </c>
       <c r="F52">
-        <v>25.8</v>
+        <v>26.316</v>
       </c>
       <c r="G52">
         <v>0.133</v>
@@ -5795,37 +5795,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M52">
-        <v>6.083640000000001</v>
+        <v>6.205312800000001</v>
       </c>
       <c r="N52">
-        <v>-5.410306666666667</v>
+        <v>-5.531979466666667</v>
       </c>
       <c r="O52">
-        <v>-1.352576666666667</v>
+        <v>-1.382994866666667</v>
       </c>
       <c r="P52">
-        <v>-4.05773</v>
+        <v>-4.1489846</v>
       </c>
       <c r="Q52">
-        <v>-2.89773</v>
+        <v>-2.9889846</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2133298717346918</v>
+        <v>0.2167488487088693</v>
       </c>
       <c r="T52">
-        <v>3.265469023295425</v>
+        <v>3.332111248260639</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02766983801364534</v>
+        <v>0.02712729217024053</v>
       </c>
       <c r="W52">
-        <v>0.2292754521963825</v>
+        <v>0.2294033845062573</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1106793520545815</v>
+        <v>0.1085091686809622</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5841,22 +5841,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2232026619655371</v>
+        <v>0.2251026619655372</v>
       </c>
       <c r="C53">
-        <v>-3.043734141321121</v>
+        <v>-3.804931868167703</v>
       </c>
       <c r="D53">
-        <v>23.13926585867888</v>
+        <v>22.8940681318323</v>
       </c>
       <c r="E53">
-        <v>12.416</v>
+        <v>12.932</v>
       </c>
       <c r="F53">
-        <v>26.316</v>
+        <v>26.832</v>
       </c>
       <c r="G53">
         <v>0.133</v>
@@ -5877,37 +5877,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M53">
-        <v>6.205312800000001</v>
+        <v>6.3269856</v>
       </c>
       <c r="N53">
-        <v>-5.531979466666667</v>
+        <v>-5.653652266666667</v>
       </c>
       <c r="O53">
-        <v>-1.382994866666667</v>
+        <v>-1.413413066666667</v>
       </c>
       <c r="P53">
-        <v>-4.1489846</v>
+        <v>-4.2402392</v>
       </c>
       <c r="Q53">
-        <v>-2.9889846</v>
+        <v>-3.080239199999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2167488487088693</v>
+        <v>0.2203102830569707</v>
       </c>
       <c r="T53">
-        <v>3.332111248260639</v>
+        <v>3.401530232599402</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02712729217024053</v>
+        <v>0.02660561347465899</v>
       </c>
       <c r="W53">
-        <v>0.2294033845062573</v>
+        <v>0.2295263963426754</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1085091686809622</v>
+        <v>0.106422453898636</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5923,22 +5923,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2251026619655372</v>
+        <v>0.2270026619655371</v>
       </c>
       <c r="C54">
-        <v>-3.804931868167703</v>
+        <v>-4.56098755487033</v>
       </c>
       <c r="D54">
-        <v>22.8940681318323</v>
+        <v>22.65401244512967</v>
       </c>
       <c r="E54">
-        <v>12.932</v>
+        <v>13.448</v>
       </c>
       <c r="F54">
-        <v>26.832</v>
+        <v>27.348</v>
       </c>
       <c r="G54">
         <v>0.133</v>
@@ -5959,37 +5959,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M54">
-        <v>6.3269856</v>
+        <v>6.448658400000001</v>
       </c>
       <c r="N54">
-        <v>-5.653652266666667</v>
+        <v>-5.775325066666667</v>
       </c>
       <c r="O54">
-        <v>-1.413413066666667</v>
+        <v>-1.443831266666667</v>
       </c>
       <c r="P54">
-        <v>-4.2402392</v>
+        <v>-4.331493800000001</v>
       </c>
       <c r="Q54">
-        <v>-3.080239199999999</v>
+        <v>-3.1714938</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2203102830569707</v>
+        <v>0.2240232678028637</v>
       </c>
       <c r="T54">
-        <v>3.401530232599402</v>
+        <v>3.473903216271729</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02660561347465899</v>
+        <v>0.02610362076758995</v>
       </c>
       <c r="W54">
-        <v>0.2295263963426754</v>
+        <v>0.2296447662230023</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.106422453898636</v>
+        <v>0.1044144830703598</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6005,22 +6005,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2270026619655371</v>
+        <v>0.2289026619655372</v>
       </c>
       <c r="C55">
-        <v>-4.56098755487033</v>
+        <v>-5.312061273535591</v>
       </c>
       <c r="D55">
-        <v>22.65401244512967</v>
+        <v>22.41893872646441</v>
       </c>
       <c r="E55">
-        <v>13.448</v>
+        <v>13.96400000000001</v>
       </c>
       <c r="F55">
-        <v>27.348</v>
+        <v>27.864</v>
       </c>
       <c r="G55">
         <v>0.133</v>
@@ -6041,37 +6041,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M55">
-        <v>6.448658400000001</v>
+        <v>6.570331200000001</v>
       </c>
       <c r="N55">
-        <v>-5.775325066666667</v>
+        <v>-5.896997866666667</v>
       </c>
       <c r="O55">
-        <v>-1.443831266666667</v>
+        <v>-1.474249466666667</v>
       </c>
       <c r="P55">
-        <v>-4.331493800000001</v>
+        <v>-4.422748400000001</v>
       </c>
       <c r="Q55">
-        <v>-3.1714938</v>
+        <v>-3.2627484</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2240232678028637</v>
+        <v>0.2278976866681433</v>
       </c>
       <c r="T55">
-        <v>3.473903216271729</v>
+        <v>3.549422851408071</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02610362076758995</v>
+        <v>0.02562022038300495</v>
       </c>
       <c r="W55">
-        <v>0.2296447662230023</v>
+        <v>0.2297587520336875</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1044144830703598</v>
+        <v>0.1024808815320198</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6087,22 +6087,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2289026619655372</v>
+        <v>0.2308026619655372</v>
       </c>
       <c r="C56">
-        <v>-5.312061273535591</v>
+        <v>-6.058306520429479</v>
       </c>
       <c r="D56">
-        <v>22.41893872646441</v>
+        <v>22.18869347957052</v>
       </c>
       <c r="E56">
-        <v>13.96400000000001</v>
+        <v>14.48</v>
       </c>
       <c r="F56">
-        <v>27.864</v>
+        <v>28.38</v>
       </c>
       <c r="G56">
         <v>0.133</v>
@@ -6123,37 +6123,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M56">
-        <v>6.570331200000001</v>
+        <v>6.692004000000001</v>
       </c>
       <c r="N56">
-        <v>-5.896997866666667</v>
+        <v>-6.018670666666667</v>
       </c>
       <c r="O56">
-        <v>-1.474249466666667</v>
+        <v>-1.504667666666667</v>
       </c>
       <c r="P56">
-        <v>-4.422748400000001</v>
+        <v>-4.514003000000001</v>
       </c>
       <c r="Q56">
-        <v>-3.2627484</v>
+        <v>-3.354003000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2278976866681433</v>
+        <v>0.2319443019274354</v>
       </c>
       <c r="T56">
-        <v>3.549422851408071</v>
+        <v>3.628298914772695</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02562022038300495</v>
+        <v>0.02515439819422304</v>
       </c>
       <c r="W56">
-        <v>0.2297587520336875</v>
+        <v>0.2298685929058022</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1024808815320198</v>
+        <v>0.1006175927768922</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6169,22 +6169,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2308026619655372</v>
+        <v>0.2327026619655371</v>
       </c>
       <c r="C57">
-        <v>-6.058306520429479</v>
+        <v>-6.799870550218188</v>
       </c>
       <c r="D57">
-        <v>22.18869347957052</v>
+        <v>21.96312944978182</v>
       </c>
       <c r="E57">
-        <v>14.48</v>
+        <v>14.99600000000001</v>
       </c>
       <c r="F57">
-        <v>28.38</v>
+        <v>28.896</v>
       </c>
       <c r="G57">
         <v>0.133</v>
@@ -6205,37 +6205,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M57">
-        <v>6.692004000000001</v>
+        <v>6.813676800000001</v>
       </c>
       <c r="N57">
-        <v>-6.018670666666667</v>
+        <v>-6.140343466666668</v>
       </c>
       <c r="O57">
-        <v>-1.504667666666667</v>
+        <v>-1.535085866666667</v>
       </c>
       <c r="P57">
-        <v>-4.514003000000001</v>
+        <v>-4.605257600000001</v>
       </c>
       <c r="Q57">
-        <v>-3.354003000000001</v>
+        <v>-3.445257600000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2319443019274354</v>
+        <v>0.236174854243968</v>
       </c>
       <c r="T57">
-        <v>3.628298914772695</v>
+        <v>3.710760253744802</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02515439819422304</v>
+        <v>0.02470521251218334</v>
       </c>
       <c r="W57">
-        <v>0.2298685929058022</v>
+        <v>0.2299745108896272</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1006175927768922</v>
+        <v>0.09882085004873342</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6251,22 +6251,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2327026619655371</v>
+        <v>0.2346026619655372</v>
       </c>
       <c r="C58">
-        <v>-6.799870550218188</v>
+        <v>-7.536894690027211</v>
       </c>
       <c r="D58">
-        <v>21.96312944978182</v>
+        <v>21.74210530997279</v>
       </c>
       <c r="E58">
-        <v>14.99600000000001</v>
+        <v>15.512</v>
       </c>
       <c r="F58">
-        <v>28.896</v>
+        <v>29.412</v>
       </c>
       <c r="G58">
         <v>0.133</v>
@@ -6287,37 +6287,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M58">
-        <v>6.813676800000001</v>
+        <v>6.935349600000001</v>
       </c>
       <c r="N58">
-        <v>-6.140343466666668</v>
+        <v>-6.262016266666667</v>
       </c>
       <c r="O58">
-        <v>-1.535085866666667</v>
+        <v>-1.565504066666667</v>
       </c>
       <c r="P58">
-        <v>-4.605257600000001</v>
+        <v>-4.696512200000001</v>
       </c>
       <c r="Q58">
-        <v>-3.445257600000001</v>
+        <v>-3.536512200000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.236174854243968</v>
+        <v>0.2406021764356882</v>
       </c>
       <c r="T58">
-        <v>3.710760253744802</v>
+        <v>3.79705700383189</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02470521251218334</v>
+        <v>0.02427178773126784</v>
       </c>
       <c r="W58">
-        <v>0.2299745108896272</v>
+        <v>0.2300767124529671</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.09882085004873342</v>
+        <v>0.09708715092507136</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6333,22 +6333,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2346026619655372</v>
+        <v>0.2365026619655372</v>
       </c>
       <c r="C59">
-        <v>-7.536894690027211</v>
+        <v>-8.269514634726324</v>
       </c>
       <c r="D59">
-        <v>21.74210530997279</v>
+        <v>21.52548536527368</v>
       </c>
       <c r="E59">
-        <v>15.512</v>
+        <v>16.02800000000001</v>
       </c>
       <c r="F59">
-        <v>29.412</v>
+        <v>29.928</v>
       </c>
       <c r="G59">
         <v>0.133</v>
@@ -6369,37 +6369,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M59">
-        <v>6.935349600000001</v>
+        <v>7.057022400000001</v>
       </c>
       <c r="N59">
-        <v>-6.262016266666667</v>
+        <v>-6.383689066666667</v>
       </c>
       <c r="O59">
-        <v>-1.565504066666667</v>
+        <v>-1.595922266666667</v>
       </c>
       <c r="P59">
-        <v>-4.696512200000001</v>
+        <v>-4.7877668</v>
       </c>
       <c r="Q59">
-        <v>-3.536512200000001</v>
+        <v>-3.6277668</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2406021764356882</v>
+        <v>0.2452403234936808</v>
       </c>
       <c r="T59">
-        <v>3.79705700383189</v>
+        <v>3.887463122970745</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02427178773126784</v>
+        <v>0.02385330863245288</v>
       </c>
       <c r="W59">
-        <v>0.2300767124529671</v>
+        <v>0.2301753898244676</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09708715092507136</v>
+        <v>0.09541323452981154</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6415,22 +6415,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2365026619655372</v>
+        <v>0.2384026619655371</v>
       </c>
       <c r="C60">
-        <v>-8.269514634726317</v>
+        <v>-8.997860724736945</v>
       </c>
       <c r="D60">
-        <v>21.52548536527368</v>
+        <v>21.31313927526305</v>
       </c>
       <c r="E60">
-        <v>16.028</v>
+        <v>16.544</v>
       </c>
       <c r="F60">
-        <v>29.928</v>
+        <v>30.444</v>
       </c>
       <c r="G60">
         <v>0.133</v>
@@ -6451,37 +6451,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M60">
-        <v>7.057022399999999</v>
+        <v>7.1786952</v>
       </c>
       <c r="N60">
-        <v>-6.383689066666665</v>
+        <v>-6.505361866666666</v>
       </c>
       <c r="O60">
-        <v>-1.595922266666666</v>
+        <v>-1.626340466666667</v>
       </c>
       <c r="P60">
-        <v>-4.787766799999999</v>
+        <v>-4.879021399999999</v>
       </c>
       <c r="Q60">
-        <v>-3.627766799999999</v>
+        <v>-3.719021399999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2452403234936808</v>
+        <v>0.2501047216276729</v>
       </c>
       <c r="T60">
-        <v>3.887463122970744</v>
+        <v>3.982279296701738</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02385330863245289</v>
+        <v>0.02344901526580114</v>
       </c>
       <c r="W60">
-        <v>0.2301753898244676</v>
+        <v>0.2302707222003241</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09541323452981154</v>
+        <v>0.09379606106320459</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6497,22 +6497,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2384026619655371</v>
+        <v>0.2403026619655372</v>
       </c>
       <c r="C61">
-        <v>-8.997860724736945</v>
+        <v>-9.722058207556874</v>
       </c>
       <c r="D61">
-        <v>21.31313927526305</v>
+        <v>21.10494179244313</v>
       </c>
       <c r="E61">
-        <v>16.544</v>
+        <v>17.06</v>
       </c>
       <c r="F61">
-        <v>30.444</v>
+        <v>30.96</v>
       </c>
       <c r="G61">
         <v>0.133</v>
@@ -6533,37 +6533,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M61">
-        <v>7.1786952</v>
+        <v>7.300368000000001</v>
       </c>
       <c r="N61">
-        <v>-6.505361866666666</v>
+        <v>-6.627034666666667</v>
       </c>
       <c r="O61">
-        <v>-1.626340466666667</v>
+        <v>-1.656758666666667</v>
       </c>
       <c r="P61">
-        <v>-4.879021399999999</v>
+        <v>-4.970276</v>
       </c>
       <c r="Q61">
-        <v>-3.719021399999999</v>
+        <v>-3.810276</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2501047216276729</v>
+        <v>0.2552123396683648</v>
       </c>
       <c r="T61">
-        <v>3.982279296701738</v>
+        <v>4.081836279119281</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02344901526580114</v>
+        <v>0.02305819834470445</v>
       </c>
       <c r="W61">
-        <v>0.2302707222003241</v>
+        <v>0.2303628768303187</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09379606106320459</v>
+        <v>0.09223279337881785</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2403026619655372</v>
+        <v>0.2422026619655371</v>
       </c>
       <c r="C62">
-        <v>-9.722058207556874</v>
+        <v>-10.44222748410506</v>
       </c>
       <c r="D62">
-        <v>21.10494179244313</v>
+        <v>20.90077251589494</v>
       </c>
       <c r="E62">
-        <v>17.06</v>
+        <v>17.576</v>
       </c>
       <c r="F62">
-        <v>30.96</v>
+        <v>31.476</v>
       </c>
       <c r="G62">
         <v>0.133</v>
@@ -6615,37 +6615,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M62">
-        <v>7.300368000000001</v>
+        <v>7.4220408</v>
       </c>
       <c r="N62">
-        <v>-6.627034666666667</v>
+        <v>-6.748707466666667</v>
       </c>
       <c r="O62">
-        <v>-1.656758666666667</v>
+        <v>-1.687176866666667</v>
       </c>
       <c r="P62">
-        <v>-4.970276</v>
+        <v>-5.0615306</v>
       </c>
       <c r="Q62">
-        <v>-3.810276</v>
+        <v>-3.9015306</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2552123396683648</v>
+        <v>0.2605818868393485</v>
       </c>
       <c r="T62">
-        <v>4.081836279119281</v>
+        <v>4.186498747814648</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02305819834470445</v>
+        <v>0.02268019509315192</v>
       </c>
       <c r="W62">
-        <v>0.2303628768303187</v>
+        <v>0.2304520099970348</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09223279337881785</v>
+        <v>0.09072078037260778</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6661,22 +6661,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2422026619655371</v>
+        <v>0.2441026619655371</v>
       </c>
       <c r="C63">
-        <v>-10.44222748410506</v>
+        <v>-11.1584843409046</v>
       </c>
       <c r="D63">
-        <v>20.90077251589494</v>
+        <v>20.70051565909541</v>
       </c>
       <c r="E63">
-        <v>17.576</v>
+        <v>18.092</v>
       </c>
       <c r="F63">
-        <v>31.476</v>
+        <v>31.992</v>
       </c>
       <c r="G63">
         <v>0.133</v>
@@ -6697,37 +6697,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M63">
-        <v>7.4220408</v>
+        <v>7.5437136</v>
       </c>
       <c r="N63">
-        <v>-6.748707466666667</v>
+        <v>-6.870380266666666</v>
       </c>
       <c r="O63">
-        <v>-1.687176866666667</v>
+        <v>-1.717595066666667</v>
       </c>
       <c r="P63">
-        <v>-5.0615306</v>
+        <v>-5.1527852</v>
       </c>
       <c r="Q63">
-        <v>-3.9015306</v>
+        <v>-3.9927852</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2605818868393485</v>
+        <v>0.2662340417561734</v>
       </c>
       <c r="T63">
-        <v>4.186498747814648</v>
+        <v>4.29666976749398</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02268019509315192</v>
+        <v>0.02231438549487528</v>
       </c>
       <c r="W63">
-        <v>0.2304520099970348</v>
+        <v>0.2305382679003084</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09072078037260778</v>
+        <v>0.0892575419795012</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6743,22 +6743,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2441026619655371</v>
+        <v>0.2460026619655372</v>
       </c>
       <c r="C64">
-        <v>-11.1584843409046</v>
+        <v>-11.87094016904465</v>
       </c>
       <c r="D64">
-        <v>20.70051565909541</v>
+        <v>20.50405983095536</v>
       </c>
       <c r="E64">
-        <v>18.092</v>
+        <v>18.608</v>
       </c>
       <c r="F64">
-        <v>31.992</v>
+        <v>32.508</v>
       </c>
       <c r="G64">
         <v>0.133</v>
@@ -6779,37 +6779,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M64">
-        <v>7.5437136</v>
+        <v>7.665386400000001</v>
       </c>
       <c r="N64">
-        <v>-6.870380266666666</v>
+        <v>-6.992053066666667</v>
       </c>
       <c r="O64">
-        <v>-1.717595066666667</v>
+        <v>-1.748013266666667</v>
       </c>
       <c r="P64">
-        <v>-5.1527852</v>
+        <v>-5.2440398</v>
       </c>
       <c r="Q64">
-        <v>-3.9927852</v>
+        <v>-4.0840398</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2662340417561734</v>
+        <v>0.2721917185603944</v>
       </c>
       <c r="T64">
-        <v>4.29666976749398</v>
+        <v>4.412795977426251</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02231438549487528</v>
+        <v>0.02196018889971853</v>
       </c>
       <c r="W64">
-        <v>0.2305382679003084</v>
+        <v>0.2306217874574464</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0892575419795012</v>
+        <v>0.08784075559887417</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6825,22 +6825,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2460026619655372</v>
+        <v>0.2479026619655371</v>
       </c>
       <c r="C65">
-        <v>-11.87094016904465</v>
+        <v>-12.57970217079135</v>
       </c>
       <c r="D65">
-        <v>20.50405983095536</v>
+        <v>20.31129782920865</v>
       </c>
       <c r="E65">
-        <v>18.608</v>
+        <v>19.124</v>
       </c>
       <c r="F65">
-        <v>32.508</v>
+        <v>33.024</v>
       </c>
       <c r="G65">
         <v>0.133</v>
@@ -6861,37 +6861,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M65">
-        <v>7.665386400000001</v>
+        <v>7.787059200000001</v>
       </c>
       <c r="N65">
-        <v>-6.992053066666667</v>
+        <v>-7.113725866666667</v>
       </c>
       <c r="O65">
-        <v>-1.748013266666667</v>
+        <v>-1.778431466666667</v>
       </c>
       <c r="P65">
-        <v>-5.2440398</v>
+        <v>-5.3352944</v>
       </c>
       <c r="Q65">
-        <v>-4.0840398</v>
+        <v>-4.1752944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2721917185603944</v>
+        <v>0.2784803774092943</v>
       </c>
       <c r="T65">
-        <v>4.412795977426251</v>
+        <v>4.535373643465869</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02196018889971853</v>
+        <v>0.02161706094816043</v>
       </c>
       <c r="W65">
-        <v>0.2306217874574464</v>
+        <v>0.2307026970284238</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.08784075559887417</v>
+        <v>0.08646824379264173</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6907,22 +6907,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2479026619655371</v>
+        <v>0.2498026619655371</v>
       </c>
       <c r="C66">
-        <v>-12.57970217079135</v>
+        <v>-13.28487355465307</v>
       </c>
       <c r="D66">
-        <v>20.31129782920865</v>
+        <v>20.12212644534693</v>
       </c>
       <c r="E66">
-        <v>19.124</v>
+        <v>19.64</v>
       </c>
       <c r="F66">
-        <v>33.024</v>
+        <v>33.54</v>
       </c>
       <c r="G66">
         <v>0.133</v>
@@ -6943,37 +6943,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M66">
-        <v>7.787059200000001</v>
+        <v>7.908732000000001</v>
       </c>
       <c r="N66">
-        <v>-7.113725866666667</v>
+        <v>-7.235398666666667</v>
       </c>
       <c r="O66">
-        <v>-1.778431466666667</v>
+        <v>-1.808849666666667</v>
       </c>
       <c r="P66">
-        <v>-5.3352944</v>
+        <v>-5.426549</v>
       </c>
       <c r="Q66">
-        <v>-4.1752944</v>
+        <v>-4.266548999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2784803774092943</v>
+        <v>0.285128388192417</v>
       </c>
       <c r="T66">
-        <v>4.535373643465869</v>
+        <v>4.664955747564894</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02161706094816043</v>
+        <v>0.02128449077972719</v>
       </c>
       <c r="W66">
-        <v>0.2307026970284238</v>
+        <v>0.2307811170741403</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08646824379264173</v>
+        <v>0.08513796311890875</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6989,22 +6989,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2498026619655371</v>
+        <v>0.2517026619655371</v>
       </c>
       <c r="C67">
-        <v>-13.28487355465307</v>
+        <v>-13.9865537196456</v>
       </c>
       <c r="D67">
-        <v>20.12212644534693</v>
+        <v>19.93644628035441</v>
       </c>
       <c r="E67">
-        <v>19.64</v>
+        <v>20.15600000000001</v>
       </c>
       <c r="F67">
-        <v>33.54</v>
+        <v>34.056</v>
       </c>
       <c r="G67">
         <v>0.133</v>
@@ -7025,37 +7025,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M67">
-        <v>7.908732000000001</v>
+        <v>8.030404800000001</v>
       </c>
       <c r="N67">
-        <v>-7.235398666666667</v>
+        <v>-7.357071466666667</v>
       </c>
       <c r="O67">
-        <v>-1.808849666666667</v>
+        <v>-1.839267866666667</v>
       </c>
       <c r="P67">
-        <v>-5.426549</v>
+        <v>-5.517803600000001</v>
       </c>
       <c r="Q67">
-        <v>-4.266548999999999</v>
+        <v>-4.3578036</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.285128388192417</v>
+        <v>0.2921674584333703</v>
       </c>
       <c r="T67">
-        <v>4.664955747564894</v>
+        <v>4.802160328375625</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02128449077972719</v>
+        <v>0.02096199849518587</v>
       </c>
       <c r="W67">
-        <v>0.2307811170741403</v>
+        <v>0.2308571607548352</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08513796311890875</v>
+        <v>0.0838479939807435</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7071,22 +7071,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2517026619655371</v>
+        <v>0.2536026619655372</v>
       </c>
       <c r="C68">
-        <v>-13.9865537196456</v>
+        <v>-14.68483842944857</v>
       </c>
       <c r="D68">
-        <v>19.93644628035441</v>
+        <v>19.75416157055143</v>
       </c>
       <c r="E68">
-        <v>20.15600000000001</v>
+        <v>20.672</v>
       </c>
       <c r="F68">
-        <v>34.056</v>
+        <v>34.572</v>
       </c>
       <c r="G68">
         <v>0.133</v>
@@ -7107,37 +7107,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M68">
-        <v>8.030404800000001</v>
+        <v>8.1520776</v>
       </c>
       <c r="N68">
-        <v>-7.357071466666667</v>
+        <v>-7.478744266666666</v>
       </c>
       <c r="O68">
-        <v>-1.839267866666667</v>
+        <v>-1.869686066666667</v>
       </c>
       <c r="P68">
-        <v>-5.517803600000001</v>
+        <v>-5.6090582</v>
       </c>
       <c r="Q68">
-        <v>-4.3578036</v>
+        <v>-4.4490582</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2921674584333703</v>
+        <v>0.2996331389919574</v>
       </c>
       <c r="T68">
-        <v>4.802160328375625</v>
+        <v>4.947680338326403</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02096199849518587</v>
+        <v>0.02064913284600399</v>
       </c>
       <c r="W68">
-        <v>0.2308571607548352</v>
+        <v>0.2309309344749123</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.0838479939807435</v>
+        <v>0.08259653138401601</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7153,22 +7153,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2536026619655372</v>
+        <v>0.2555026619655371</v>
       </c>
       <c r="C69">
-        <v>-14.68483842944857</v>
+        <v>-15.37981997709442</v>
       </c>
       <c r="D69">
-        <v>19.75416157055143</v>
+        <v>19.57518002290558</v>
       </c>
       <c r="E69">
-        <v>20.672</v>
+        <v>21.188</v>
       </c>
       <c r="F69">
-        <v>34.572</v>
+        <v>35.088</v>
       </c>
       <c r="G69">
         <v>0.133</v>
@@ -7189,37 +7189,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M69">
-        <v>8.1520776</v>
+        <v>8.273750400000001</v>
       </c>
       <c r="N69">
-        <v>-7.478744266666666</v>
+        <v>-7.600417066666667</v>
       </c>
       <c r="O69">
-        <v>-1.869686066666667</v>
+        <v>-1.900104266666667</v>
       </c>
       <c r="P69">
-        <v>-5.6090582</v>
+        <v>-5.700312800000001</v>
       </c>
       <c r="Q69">
-        <v>-4.4490582</v>
+        <v>-4.540312800000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2996331389919574</v>
+        <v>0.307565424585456</v>
       </c>
       <c r="T69">
-        <v>4.947680338326403</v>
+        <v>5.102295348899102</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02064913284600399</v>
+        <v>0.0203454691276804</v>
       </c>
       <c r="W69">
-        <v>0.2309309344749123</v>
+        <v>0.231002538379693</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08259653138401601</v>
+        <v>0.0813818765107216</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7235,22 +7235,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2555026619655371</v>
+        <v>0.2574026619655372</v>
       </c>
       <c r="C70">
-        <v>-15.37981997709442</v>
+        <v>-16.07158734078468</v>
       </c>
       <c r="D70">
-        <v>19.57518002290558</v>
+        <v>19.39941265921533</v>
       </c>
       <c r="E70">
-        <v>21.188</v>
+        <v>21.70400000000001</v>
       </c>
       <c r="F70">
-        <v>35.088</v>
+        <v>35.60400000000001</v>
       </c>
       <c r="G70">
         <v>0.133</v>
@@ -7271,37 +7271,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M70">
-        <v>8.273750400000001</v>
+        <v>8.395423200000002</v>
       </c>
       <c r="N70">
-        <v>-7.600417066666667</v>
+        <v>-7.722089866666668</v>
       </c>
       <c r="O70">
-        <v>-1.900104266666667</v>
+        <v>-1.930522466666667</v>
       </c>
       <c r="P70">
-        <v>-5.700312800000001</v>
+        <v>-5.791567400000001</v>
       </c>
       <c r="Q70">
-        <v>-4.540312800000001</v>
+        <v>-4.631567400000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.307565424585456</v>
+        <v>0.3160094705398256</v>
       </c>
       <c r="T70">
-        <v>5.102295348899102</v>
+        <v>5.266885521444236</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0203454691276804</v>
+        <v>0.02005060725626474</v>
       </c>
       <c r="W70">
-        <v>0.231002538379693</v>
+        <v>0.2310720668089728</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0813818765107216</v>
+        <v>0.08020242902505903</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7317,22 +7317,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2574026619655372</v>
+        <v>0.2593026619655371</v>
       </c>
       <c r="C71">
-        <v>-16.07158734078468</v>
+        <v>-16.76022633138638</v>
       </c>
       <c r="D71">
-        <v>19.39941265921533</v>
+        <v>19.22677366861362</v>
       </c>
       <c r="E71">
-        <v>21.70400000000001</v>
+        <v>22.22000000000001</v>
       </c>
       <c r="F71">
-        <v>35.60400000000001</v>
+        <v>36.12</v>
       </c>
       <c r="G71">
         <v>0.133</v>
@@ -7353,37 +7353,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M71">
-        <v>8.395423200000002</v>
+        <v>8.517096000000002</v>
       </c>
       <c r="N71">
-        <v>-7.722089866666668</v>
+        <v>-7.843762666666668</v>
       </c>
       <c r="O71">
-        <v>-1.930522466666667</v>
+        <v>-1.960940666666667</v>
       </c>
       <c r="P71">
-        <v>-5.791567400000001</v>
+        <v>-5.882822000000001</v>
       </c>
       <c r="Q71">
-        <v>-4.631567400000001</v>
+        <v>-4.722822000000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3160094705398256</v>
+        <v>0.3250164528911531</v>
       </c>
       <c r="T71">
-        <v>5.266885521444236</v>
+        <v>5.442448372159043</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02005060725626474</v>
+        <v>0.01976417000974667</v>
       </c>
       <c r="W71">
-        <v>0.2310720668089728</v>
+        <v>0.2311396087117017</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08020242902505903</v>
+        <v>0.07905668003898669</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7399,22 +7399,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2593026619655371</v>
+        <v>0.2612026619655372</v>
       </c>
       <c r="C72">
-        <v>-16.76022633138638</v>
+        <v>-17.44581973212259</v>
       </c>
       <c r="D72">
-        <v>19.22677366861362</v>
+        <v>19.05718026787742</v>
       </c>
       <c r="E72">
-        <v>22.22000000000001</v>
+        <v>22.736</v>
       </c>
       <c r="F72">
-        <v>36.12</v>
+        <v>36.636</v>
       </c>
       <c r="G72">
         <v>0.133</v>
@@ -7435,37 +7435,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M72">
-        <v>8.517096000000002</v>
+        <v>8.638768800000001</v>
       </c>
       <c r="N72">
-        <v>-7.843762666666668</v>
+        <v>-7.965435466666667</v>
       </c>
       <c r="O72">
-        <v>-1.960940666666667</v>
+        <v>-1.991358866666667</v>
       </c>
       <c r="P72">
-        <v>-5.882822000000001</v>
+        <v>-5.9740766</v>
       </c>
       <c r="Q72">
-        <v>-4.722822000000001</v>
+        <v>-4.8140766</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3250164528911531</v>
+        <v>0.334644606439124</v>
       </c>
       <c r="T72">
-        <v>5.442448372159043</v>
+        <v>5.630119005681769</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01976417000974667</v>
+        <v>0.0194858014180601</v>
       </c>
       <c r="W72">
-        <v>0.2311396087117017</v>
+        <v>0.2312052480256214</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.07905668003898669</v>
+        <v>0.07794320567224045</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7481,22 +7481,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2612026619655372</v>
+        <v>0.2631026619655371</v>
       </c>
       <c r="C73">
-        <v>-17.44581973212258</v>
+        <v>-18.12844743093424</v>
       </c>
       <c r="D73">
-        <v>19.05718026787742</v>
+        <v>18.89055256906576</v>
       </c>
       <c r="E73">
-        <v>22.736</v>
+        <v>23.252</v>
       </c>
       <c r="F73">
-        <v>36.636</v>
+        <v>37.152</v>
       </c>
       <c r="G73">
         <v>0.133</v>
@@ -7517,37 +7517,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M73">
-        <v>8.638768799999999</v>
+        <v>8.7604416</v>
       </c>
       <c r="N73">
-        <v>-7.965435466666666</v>
+        <v>-8.087108266666666</v>
       </c>
       <c r="O73">
-        <v>-1.991358866666666</v>
+        <v>-2.021777066666667</v>
       </c>
       <c r="P73">
-        <v>-5.974076599999999</v>
+        <v>-6.065331199999999</v>
       </c>
       <c r="Q73">
-        <v>-4.814076599999999</v>
+        <v>-4.905331199999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3346446064391239</v>
+        <v>0.3449604852405211</v>
       </c>
       <c r="T73">
-        <v>5.630119005681768</v>
+        <v>5.831194684456116</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01948580141806011</v>
+        <v>0.01921516528725371</v>
       </c>
       <c r="W73">
-        <v>0.2312052480256214</v>
+        <v>0.2312690640252656</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07794320567224045</v>
+        <v>0.07686066114901491</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7563,22 +7563,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2631026619655371</v>
+        <v>0.2650026619655371</v>
       </c>
       <c r="C74">
-        <v>-18.12844743093424</v>
+        <v>-18.80818654595863</v>
       </c>
       <c r="D74">
-        <v>18.89055256906576</v>
+        <v>18.72681345404137</v>
       </c>
       <c r="E74">
-        <v>23.252</v>
+        <v>23.768</v>
       </c>
       <c r="F74">
-        <v>37.152</v>
+        <v>37.668</v>
       </c>
       <c r="G74">
         <v>0.133</v>
@@ -7599,37 +7599,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M74">
-        <v>8.7604416</v>
+        <v>8.882114400000001</v>
       </c>
       <c r="N74">
-        <v>-8.087108266666666</v>
+        <v>-8.208781066666667</v>
       </c>
       <c r="O74">
-        <v>-2.021777066666667</v>
+        <v>-2.052195266666667</v>
       </c>
       <c r="P74">
-        <v>-6.065331199999999</v>
+        <v>-6.1565858</v>
       </c>
       <c r="Q74">
-        <v>-4.905331199999999</v>
+        <v>-4.9965858</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3449604852405211</v>
+        <v>0.3560405032123923</v>
       </c>
       <c r="T74">
-        <v>5.831194684456116</v>
+        <v>6.047164857954491</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01921516528725371</v>
+        <v>0.01895194384496257</v>
       </c>
       <c r="W74">
-        <v>0.2312690640252656</v>
+        <v>0.2313311316413578</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07686066114901491</v>
+        <v>0.07580777537985028</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7645,22 +7645,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2650026619655371</v>
+        <v>0.2669026619655371</v>
       </c>
       <c r="C75">
-        <v>-18.80818654595863</v>
+        <v>-19.4851115445379</v>
       </c>
       <c r="D75">
-        <v>18.72681345404137</v>
+        <v>18.5658884554621</v>
       </c>
       <c r="E75">
-        <v>23.768</v>
+        <v>24.284</v>
       </c>
       <c r="F75">
-        <v>37.668</v>
+        <v>38.184</v>
       </c>
       <c r="G75">
         <v>0.133</v>
@@ -7681,37 +7681,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M75">
-        <v>8.882114400000001</v>
+        <v>9.0037872</v>
       </c>
       <c r="N75">
-        <v>-8.208781066666667</v>
+        <v>-8.330453866666666</v>
       </c>
       <c r="O75">
-        <v>-2.052195266666667</v>
+        <v>-2.082613466666666</v>
       </c>
       <c r="P75">
-        <v>-6.1565858</v>
+        <v>-6.247840399999999</v>
       </c>
       <c r="Q75">
-        <v>-4.9965858</v>
+        <v>-5.087840399999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3560405032123923</v>
+        <v>0.3679728302590228</v>
       </c>
       <c r="T75">
-        <v>6.047164857954491</v>
+        <v>6.279748121721972</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01895194384496257</v>
+        <v>0.01869583649570632</v>
       </c>
       <c r="W75">
-        <v>0.2313311316413578</v>
+        <v>0.2313915217543125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07580777537985028</v>
+        <v>0.07478334598282532</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7727,22 +7727,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2669026619655371</v>
+        <v>0.2688026619655371</v>
       </c>
       <c r="C76">
-        <v>-19.4851115445379</v>
+        <v>-20.15929435614412</v>
       </c>
       <c r="D76">
-        <v>18.5658884554621</v>
+        <v>18.40770564385588</v>
       </c>
       <c r="E76">
-        <v>24.284</v>
+        <v>24.8</v>
       </c>
       <c r="F76">
-        <v>38.184</v>
+        <v>38.7</v>
       </c>
       <c r="G76">
         <v>0.133</v>
@@ -7763,37 +7763,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M76">
-        <v>9.0037872</v>
+        <v>9.12546</v>
       </c>
       <c r="N76">
-        <v>-8.330453866666666</v>
+        <v>-8.452126666666667</v>
       </c>
       <c r="O76">
-        <v>-2.082613466666666</v>
+        <v>-2.113031666666667</v>
       </c>
       <c r="P76">
-        <v>-6.247840399999999</v>
+        <v>-6.339095</v>
       </c>
       <c r="Q76">
-        <v>-5.087840399999999</v>
+        <v>-5.179095</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3679728302590228</v>
+        <v>0.3808597434693837</v>
       </c>
       <c r="T76">
-        <v>6.279748121721972</v>
+        <v>6.53093804659085</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01869583649570632</v>
+        <v>0.01844655867576356</v>
       </c>
       <c r="W76">
-        <v>0.2313915217543125</v>
+        <v>0.2314503014642549</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07478334598282532</v>
+        <v>0.07378623470305423</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7809,22 +7809,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2688026619655371</v>
+        <v>0.2707026619655372</v>
       </c>
       <c r="C77">
-        <v>-20.15929435614412</v>
+        <v>-20.83080447958003</v>
       </c>
       <c r="D77">
-        <v>18.40770564385588</v>
+        <v>18.25219552041997</v>
       </c>
       <c r="E77">
-        <v>24.8</v>
+        <v>25.316</v>
       </c>
       <c r="F77">
-        <v>38.7</v>
+        <v>39.216</v>
       </c>
       <c r="G77">
         <v>0.133</v>
@@ -7845,37 +7845,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M77">
-        <v>9.12546</v>
+        <v>9.247132800000001</v>
       </c>
       <c r="N77">
-        <v>-8.452126666666667</v>
+        <v>-8.573799466666667</v>
       </c>
       <c r="O77">
-        <v>-2.113031666666667</v>
+        <v>-2.143449866666667</v>
       </c>
       <c r="P77">
-        <v>-6.339095</v>
+        <v>-6.4303496</v>
       </c>
       <c r="Q77">
-        <v>-5.179095</v>
+        <v>-5.2703496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3808597434693837</v>
+        <v>0.3948205661139415</v>
       </c>
       <c r="T77">
-        <v>6.53093804659085</v>
+        <v>6.803060465198804</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01844655867576356</v>
+        <v>0.01820384079845088</v>
       </c>
       <c r="W77">
-        <v>0.2314503014642549</v>
+        <v>0.2315075343397253</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07378623470305423</v>
+        <v>0.07281536319380355</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7891,22 +7891,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2707026619655372</v>
+        <v>0.2726026619655372</v>
       </c>
       <c r="C78">
-        <v>-20.83080447958003</v>
+        <v>-21.49970908479171</v>
       </c>
       <c r="D78">
-        <v>18.25219552041997</v>
+        <v>18.09929091520829</v>
       </c>
       <c r="E78">
-        <v>25.316</v>
+        <v>25.832</v>
       </c>
       <c r="F78">
-        <v>39.216</v>
+        <v>39.732</v>
       </c>
       <c r="G78">
         <v>0.133</v>
@@ -7927,37 +7927,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M78">
-        <v>9.247132800000001</v>
+        <v>9.3688056</v>
       </c>
       <c r="N78">
-        <v>-8.573799466666667</v>
+        <v>-8.695472266666666</v>
       </c>
       <c r="O78">
-        <v>-2.143449866666667</v>
+        <v>-2.173868066666667</v>
       </c>
       <c r="P78">
-        <v>-6.4303496</v>
+        <v>-6.5216042</v>
       </c>
       <c r="Q78">
-        <v>-5.2703496</v>
+        <v>-5.361604199999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3948205661139415</v>
+        <v>0.4099953733362866</v>
       </c>
       <c r="T78">
-        <v>6.803060465198804</v>
+        <v>7.098845702816142</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01820384079845088</v>
+        <v>0.01796742728158789</v>
       </c>
       <c r="W78">
-        <v>0.2315075343397253</v>
+        <v>0.2315632806470016</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07281536319380355</v>
+        <v>0.0718697091263516</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7973,22 +7973,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2726026619655372</v>
+        <v>0.2745026619655371</v>
       </c>
       <c r="C79">
-        <v>-21.49970908479171</v>
+        <v>-22.16607310960607</v>
       </c>
       <c r="D79">
-        <v>18.09929091520829</v>
+        <v>17.94892689039393</v>
       </c>
       <c r="E79">
-        <v>25.832</v>
+        <v>26.34800000000001</v>
       </c>
       <c r="F79">
-        <v>39.732</v>
+        <v>40.248</v>
       </c>
       <c r="G79">
         <v>0.133</v>
@@ -8009,37 +8009,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M79">
-        <v>9.3688056</v>
+        <v>9.490478400000001</v>
       </c>
       <c r="N79">
-        <v>-8.695472266666666</v>
+        <v>-8.817145066666667</v>
       </c>
       <c r="O79">
-        <v>-2.173868066666667</v>
+        <v>-2.204286266666667</v>
       </c>
       <c r="P79">
-        <v>-6.5216042</v>
+        <v>-6.6128588</v>
       </c>
       <c r="Q79">
-        <v>-5.361604199999999</v>
+        <v>-5.4528588</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4099953733362866</v>
+        <v>0.4265497084879361</v>
       </c>
       <c r="T79">
-        <v>7.098845702816142</v>
+        <v>7.421520507489603</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01796742728158789</v>
+        <v>0.01773707564977266</v>
       </c>
       <c r="W79">
-        <v>0.2315632806470016</v>
+        <v>0.2316175975617836</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0718697091263516</v>
+        <v>0.07094830259909068</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8055,22 +8055,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2745026619655371</v>
+        <v>0.2764026619655372</v>
       </c>
       <c r="C80">
-        <v>-22.16607310960607</v>
+        <v>-22.82995935168616</v>
       </c>
       <c r="D80">
-        <v>17.94892689039393</v>
+        <v>17.80104064831384</v>
       </c>
       <c r="E80">
-        <v>26.34800000000001</v>
+        <v>26.864</v>
       </c>
       <c r="F80">
-        <v>40.248</v>
+        <v>40.764</v>
       </c>
       <c r="G80">
         <v>0.133</v>
@@ -8091,37 +8091,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M80">
-        <v>9.490478400000001</v>
+        <v>9.612151200000001</v>
       </c>
       <c r="N80">
-        <v>-8.817145066666667</v>
+        <v>-8.938817866666668</v>
       </c>
       <c r="O80">
-        <v>-2.204286266666667</v>
+        <v>-2.234704466666667</v>
       </c>
       <c r="P80">
-        <v>-6.6128588</v>
+        <v>-6.704113400000001</v>
       </c>
       <c r="Q80">
-        <v>-5.4528588</v>
+        <v>-5.544113400000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4265497084879361</v>
+        <v>0.4446806469873616</v>
       </c>
       <c r="T80">
-        <v>7.421520507489603</v>
+        <v>7.774926245941491</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01773707564977266</v>
+        <v>0.01751255570483883</v>
       </c>
       <c r="W80">
-        <v>0.2316175975617836</v>
+        <v>0.231670539364799</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07094830259909068</v>
+        <v>0.07005022281935536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2764026619655372</v>
+        <v>0.2783026619655372</v>
       </c>
       <c r="C81">
-        <v>-22.82995935168616</v>
+        <v>-23.49142855597772</v>
       </c>
       <c r="D81">
-        <v>17.80104064831384</v>
+        <v>17.65557144402228</v>
       </c>
       <c r="E81">
-        <v>26.864</v>
+        <v>27.38</v>
       </c>
       <c r="F81">
-        <v>40.764</v>
+        <v>41.28</v>
       </c>
       <c r="G81">
         <v>0.133</v>
@@ -8173,37 +8173,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M81">
-        <v>9.612151200000001</v>
+        <v>9.733824</v>
       </c>
       <c r="N81">
-        <v>-8.938817866666668</v>
+        <v>-9.060490666666666</v>
       </c>
       <c r="O81">
-        <v>-2.234704466666667</v>
+        <v>-2.265122666666667</v>
       </c>
       <c r="P81">
-        <v>-6.704113400000001</v>
+        <v>-6.795368</v>
       </c>
       <c r="Q81">
-        <v>-5.544113400000001</v>
+        <v>-5.635368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4446806469873616</v>
+        <v>0.4646246793367296</v>
       </c>
       <c r="T81">
-        <v>7.774926245941491</v>
+        <v>8.163672558238563</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01751255570483883</v>
+        <v>0.01729364875852834</v>
       </c>
       <c r="W81">
-        <v>0.231670539364799</v>
+        <v>0.231722157622739</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07005022281935536</v>
+        <v>0.06917459503411338</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8219,22 +8219,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2783026619655372</v>
+        <v>0.2802026619655372</v>
       </c>
       <c r="C82">
-        <v>-23.49142855597772</v>
+        <v>-24.15053949790284</v>
       </c>
       <c r="D82">
-        <v>17.65557144402228</v>
+        <v>17.51246050209717</v>
       </c>
       <c r="E82">
-        <v>27.38</v>
+        <v>27.89600000000001</v>
       </c>
       <c r="F82">
-        <v>41.28</v>
+        <v>41.79600000000001</v>
       </c>
       <c r="G82">
         <v>0.133</v>
@@ -8255,37 +8255,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M82">
-        <v>9.733824</v>
+        <v>9.855496800000003</v>
       </c>
       <c r="N82">
-        <v>-9.060490666666666</v>
+        <v>-9.182163466666669</v>
       </c>
       <c r="O82">
-        <v>-2.265122666666667</v>
+        <v>-2.295540866666667</v>
       </c>
       <c r="P82">
-        <v>-6.795368</v>
+        <v>-6.886622600000002</v>
       </c>
       <c r="Q82">
-        <v>-5.635368</v>
+        <v>-5.726622600000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4646246793367296</v>
+        <v>0.4866680835123471</v>
       </c>
       <c r="T82">
-        <v>8.163672558238563</v>
+        <v>8.593339534987964</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01729364875852834</v>
+        <v>0.0170801469220033</v>
       </c>
       <c r="W82">
-        <v>0.231722157622739</v>
+        <v>0.2317725013557916</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.06917459503411338</v>
+        <v>0.06832058768801319</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8301,22 +8301,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2802026619655372</v>
+        <v>0.2821026619655372</v>
       </c>
       <c r="C83">
-        <v>-24.15053949790284</v>
+        <v>-24.80734906254006</v>
       </c>
       <c r="D83">
-        <v>17.51246050209717</v>
+        <v>17.37165093745994</v>
       </c>
       <c r="E83">
-        <v>27.89600000000001</v>
+        <v>28.41200000000001</v>
       </c>
       <c r="F83">
-        <v>41.79600000000001</v>
+        <v>42.312</v>
       </c>
       <c r="G83">
         <v>0.133</v>
@@ -8337,37 +8337,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M83">
-        <v>9.855496800000003</v>
+        <v>9.977169600000002</v>
       </c>
       <c r="N83">
-        <v>-9.182163466666669</v>
+        <v>-9.303836266666668</v>
       </c>
       <c r="O83">
-        <v>-2.295540866666667</v>
+        <v>-2.325959066666667</v>
       </c>
       <c r="P83">
-        <v>-6.886622600000002</v>
+        <v>-6.977877200000001</v>
       </c>
       <c r="Q83">
-        <v>-5.726622600000002</v>
+        <v>-5.817877200000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4866680835123471</v>
+        <v>0.5111607548185886</v>
       </c>
       <c r="T83">
-        <v>8.593339534987964</v>
+        <v>9.07074728693174</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0170801469220033</v>
+        <v>0.01687185244734472</v>
       </c>
       <c r="W83">
-        <v>0.2317725013557916</v>
+        <v>0.2318216171929161</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06832058768801319</v>
+        <v>0.06748740978937895</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8383,22 +8383,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2821026619655372</v>
+        <v>0.2840026619655371</v>
       </c>
       <c r="C84">
-        <v>-24.80734906254006</v>
+        <v>-25.46191232001511</v>
       </c>
       <c r="D84">
-        <v>17.37165093745994</v>
+        <v>17.23308767998489</v>
       </c>
       <c r="E84">
-        <v>28.41200000000001</v>
+        <v>28.928</v>
       </c>
       <c r="F84">
-        <v>42.312</v>
+        <v>42.828</v>
       </c>
       <c r="G84">
         <v>0.133</v>
@@ -8419,37 +8419,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M84">
-        <v>9.977169600000002</v>
+        <v>10.0988424</v>
       </c>
       <c r="N84">
-        <v>-9.303836266666668</v>
+        <v>-9.425509066666667</v>
       </c>
       <c r="O84">
-        <v>-2.325959066666667</v>
+        <v>-2.356377266666667</v>
       </c>
       <c r="P84">
-        <v>-6.977877200000001</v>
+        <v>-7.0691318</v>
       </c>
       <c r="Q84">
-        <v>-5.817877200000001</v>
+        <v>-5.9091318</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5111607548185886</v>
+        <v>0.5385349168667409</v>
       </c>
       <c r="T84">
-        <v>9.07074728693174</v>
+        <v>9.604320656751256</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01687185244734472</v>
+        <v>0.01666857711665382</v>
       </c>
       <c r="W84">
-        <v>0.2318216171929161</v>
+        <v>0.231869549515893</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06748740978937895</v>
+        <v>0.06667430846661526</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8465,22 +8465,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2840026619655371</v>
+        <v>0.2859026619655372</v>
       </c>
       <c r="C85">
-        <v>-25.46191232001511</v>
+        <v>-26.11428259731205</v>
       </c>
       <c r="D85">
-        <v>17.23308767998489</v>
+        <v>17.09671740268796</v>
       </c>
       <c r="E85">
-        <v>28.928</v>
+        <v>29.44400000000001</v>
       </c>
       <c r="F85">
-        <v>42.828</v>
+        <v>43.34400000000001</v>
       </c>
       <c r="G85">
         <v>0.133</v>
@@ -8501,37 +8501,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M85">
-        <v>10.0988424</v>
+        <v>10.2205152</v>
       </c>
       <c r="N85">
-        <v>-9.425509066666667</v>
+        <v>-9.547181866666669</v>
       </c>
       <c r="O85">
-        <v>-2.356377266666667</v>
+        <v>-2.386795466666667</v>
       </c>
       <c r="P85">
-        <v>-7.0691318</v>
+        <v>-7.160386400000002</v>
       </c>
       <c r="Q85">
-        <v>-5.9091318</v>
+        <v>-6.000386400000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5385349168667409</v>
+        <v>0.5693308491709123</v>
       </c>
       <c r="T85">
-        <v>9.604320656751256</v>
+        <v>10.20459069779821</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01666857711665382</v>
+        <v>0.01647014167478889</v>
       </c>
       <c r="W85">
-        <v>0.231869549515893</v>
+        <v>0.2319163405930848</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06667430846661526</v>
+        <v>0.06588056669915554</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8547,22 +8547,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2859026619655372</v>
+        <v>0.2878026619655372</v>
       </c>
       <c r="C86">
-        <v>-26.11428259731204</v>
+        <v>-26.76451154670158</v>
       </c>
       <c r="D86">
-        <v>17.09671740268796</v>
+        <v>16.96248845329842</v>
       </c>
       <c r="E86">
-        <v>29.444</v>
+        <v>29.96</v>
       </c>
       <c r="F86">
-        <v>43.344</v>
+        <v>43.86</v>
       </c>
       <c r="G86">
         <v>0.133</v>
@@ -8583,37 +8583,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M86">
-        <v>10.2205152</v>
+        <v>10.342188</v>
       </c>
       <c r="N86">
-        <v>-9.547181866666667</v>
+        <v>-9.668854666666666</v>
       </c>
       <c r="O86">
-        <v>-2.386795466666667</v>
+        <v>-2.417213666666667</v>
       </c>
       <c r="P86">
-        <v>-7.1603864</v>
+        <v>-7.251640999999999</v>
       </c>
       <c r="Q86">
-        <v>-6.0003864</v>
+        <v>-6.091640999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5693308491709118</v>
+        <v>0.604232905782306</v>
       </c>
       <c r="T86">
-        <v>10.2045906977982</v>
+        <v>10.88489674431808</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0164701416747889</v>
+        <v>0.01627637530214432</v>
       </c>
       <c r="W86">
-        <v>0.2319163405930848</v>
+        <v>0.2319620307037544</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06588056669915565</v>
+        <v>0.06510550120857728</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8629,22 +8629,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2878026619655372</v>
+        <v>0.2897026619655371</v>
       </c>
       <c r="C87">
-        <v>-26.76451154670158</v>
+        <v>-27.41264921097119</v>
       </c>
       <c r="D87">
-        <v>16.96248845329842</v>
+        <v>16.83035078902881</v>
       </c>
       <c r="E87">
-        <v>29.96</v>
+        <v>30.476</v>
       </c>
       <c r="F87">
-        <v>43.86</v>
+        <v>44.376</v>
       </c>
       <c r="G87">
         <v>0.133</v>
@@ -8665,37 +8665,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M87">
-        <v>10.342188</v>
+        <v>10.4638608</v>
       </c>
       <c r="N87">
-        <v>-9.668854666666666</v>
+        <v>-9.790527466666665</v>
       </c>
       <c r="O87">
-        <v>-2.417213666666667</v>
+        <v>-2.447631866666666</v>
       </c>
       <c r="P87">
-        <v>-7.251640999999999</v>
+        <v>-7.342895599999999</v>
       </c>
       <c r="Q87">
-        <v>-6.091640999999999</v>
+        <v>-6.182895599999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.604232905782306</v>
+        <v>0.6441209704810422</v>
       </c>
       <c r="T87">
-        <v>10.88489674431808</v>
+        <v>11.66238936891223</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01627637530214432</v>
+        <v>0.01608711512421241</v>
       </c>
       <c r="W87">
-        <v>0.2319620307037544</v>
+        <v>0.2320066582537107</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06510550120857728</v>
+        <v>0.06434846049684972</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8711,22 +8711,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2897026619655371</v>
+        <v>0.2916026619655371</v>
       </c>
       <c r="C88">
-        <v>-27.41264921097119</v>
+        <v>-28.05874408562979</v>
       </c>
       <c r="D88">
-        <v>16.83035078902881</v>
+        <v>16.70025591437021</v>
       </c>
       <c r="E88">
-        <v>30.476</v>
+        <v>30.992</v>
       </c>
       <c r="F88">
-        <v>44.376</v>
+        <v>44.892</v>
       </c>
       <c r="G88">
         <v>0.133</v>
@@ -8747,37 +8747,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M88">
-        <v>10.4638608</v>
+        <v>10.5855336</v>
       </c>
       <c r="N88">
-        <v>-9.790527466666665</v>
+        <v>-9.912200266666668</v>
       </c>
       <c r="O88">
-        <v>-2.447631866666666</v>
+        <v>-2.478050066666667</v>
       </c>
       <c r="P88">
-        <v>-7.342895599999999</v>
+        <v>-7.434150200000001</v>
       </c>
       <c r="Q88">
-        <v>-6.182895599999998</v>
+        <v>-6.274150200000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6441209704810422</v>
+        <v>0.6901456605180454</v>
       </c>
       <c r="T88">
-        <v>11.66238936891223</v>
+        <v>12.55949624344394</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01608711512421241</v>
+        <v>0.01590220575496859</v>
       </c>
       <c r="W88">
-        <v>0.2320066582537107</v>
+        <v>0.2320502598829784</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06434846049684972</v>
+        <v>0.06360882301987436</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8793,22 +8793,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2916026619655371</v>
+        <v>0.2935026619655371</v>
       </c>
       <c r="C89">
-        <v>-28.05874408562979</v>
+        <v>-28.70284317824963</v>
       </c>
       <c r="D89">
-        <v>16.70025591437021</v>
+        <v>16.57215682175037</v>
       </c>
       <c r="E89">
-        <v>30.992</v>
+        <v>31.508</v>
       </c>
       <c r="F89">
-        <v>44.892</v>
+        <v>45.408</v>
       </c>
       <c r="G89">
         <v>0.133</v>
@@ -8829,37 +8829,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M89">
-        <v>10.5855336</v>
+        <v>10.7072064</v>
       </c>
       <c r="N89">
-        <v>-9.912200266666668</v>
+        <v>-10.03387306666667</v>
       </c>
       <c r="O89">
-        <v>-2.478050066666667</v>
+        <v>-2.508468266666667</v>
       </c>
       <c r="P89">
-        <v>-7.434150200000001</v>
+        <v>-7.5254048</v>
       </c>
       <c r="Q89">
-        <v>-6.274150200000001</v>
+        <v>-6.3654048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6901456605180454</v>
+        <v>0.7438411322278826</v>
       </c>
       <c r="T89">
-        <v>12.55949624344394</v>
+        <v>13.6061209303976</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01590220575496859</v>
+        <v>0.0157214988713894</v>
       </c>
       <c r="W89">
-        <v>0.2320502598829784</v>
+        <v>0.2320928705661264</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06360882301987436</v>
+        <v>0.06288599548555762</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8875,22 +8875,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2935026619655371</v>
+        <v>0.2954026619655371</v>
       </c>
       <c r="C90">
-        <v>-28.70284317824963</v>
+        <v>-29.34499206509792</v>
       </c>
       <c r="D90">
-        <v>16.57215682175037</v>
+        <v>16.44600793490208</v>
       </c>
       <c r="E90">
-        <v>31.508</v>
+        <v>32.024</v>
       </c>
       <c r="F90">
-        <v>45.408</v>
+        <v>45.924</v>
       </c>
       <c r="G90">
         <v>0.133</v>
@@ -8911,37 +8911,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M90">
-        <v>10.7072064</v>
+        <v>10.8288792</v>
       </c>
       <c r="N90">
-        <v>-10.03387306666667</v>
+        <v>-10.15554586666667</v>
       </c>
       <c r="O90">
-        <v>-2.508468266666667</v>
+        <v>-2.538886466666667</v>
       </c>
       <c r="P90">
-        <v>-7.5254048</v>
+        <v>-7.616659400000001</v>
       </c>
       <c r="Q90">
-        <v>-6.3654048</v>
+        <v>-6.4566594</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7438411322278826</v>
+        <v>0.807299416975872</v>
       </c>
       <c r="T90">
-        <v>13.6061209303976</v>
+        <v>14.84304101497921</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0157214988713894</v>
+        <v>0.01554485281665469</v>
       </c>
       <c r="W90">
-        <v>0.2320928705661264</v>
+        <v>0.2321345237058328</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06288599548555762</v>
+        <v>0.06217941126661874</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8957,22 +8957,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2954026619655371</v>
+        <v>0.2973026619655372</v>
       </c>
       <c r="C91">
-        <v>-29.34499206509792</v>
+        <v>-29.98523494520151</v>
       </c>
       <c r="D91">
-        <v>16.44600793490208</v>
+        <v>16.3217650547985</v>
       </c>
       <c r="E91">
-        <v>32.024</v>
+        <v>32.54000000000001</v>
       </c>
       <c r="F91">
-        <v>45.924</v>
+        <v>46.44</v>
       </c>
       <c r="G91">
         <v>0.133</v>
@@ -8993,37 +8993,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M91">
-        <v>10.8288792</v>
+        <v>10.950552</v>
       </c>
       <c r="N91">
-        <v>-10.15554586666667</v>
+        <v>-10.27721866666667</v>
       </c>
       <c r="O91">
-        <v>-2.538886466666667</v>
+        <v>-2.569304666666667</v>
       </c>
       <c r="P91">
-        <v>-7.616659400000001</v>
+        <v>-7.707914000000001</v>
       </c>
       <c r="Q91">
-        <v>-6.4566594</v>
+        <v>-6.547914</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.807299416975872</v>
+        <v>0.8834493586734593</v>
       </c>
       <c r="T91">
-        <v>14.84304101497921</v>
+        <v>16.32734511647713</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01554485281665469</v>
+        <v>0.01537213222980297</v>
       </c>
       <c r="W91">
-        <v>0.2321345237058328</v>
+        <v>0.2321752512202125</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06217941126661874</v>
+        <v>0.06148852891921186</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9039,22 +9039,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2973026619655372</v>
+        <v>0.2992026619655371</v>
       </c>
       <c r="C92">
-        <v>-29.98523494520151</v>
+        <v>-30.62361469197912</v>
       </c>
       <c r="D92">
-        <v>16.3217650547985</v>
+        <v>16.19938530802088</v>
       </c>
       <c r="E92">
-        <v>32.54000000000001</v>
+        <v>33.056</v>
       </c>
       <c r="F92">
-        <v>46.44</v>
+        <v>46.956</v>
       </c>
       <c r="G92">
         <v>0.133</v>
@@ -9075,37 +9075,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M92">
-        <v>10.950552</v>
+        <v>11.0722248</v>
       </c>
       <c r="N92">
-        <v>-10.27721866666667</v>
+        <v>-10.39889146666667</v>
       </c>
       <c r="O92">
-        <v>-2.569304666666667</v>
+        <v>-2.599722866666667</v>
       </c>
       <c r="P92">
-        <v>-7.707914000000001</v>
+        <v>-7.7991686</v>
       </c>
       <c r="Q92">
-        <v>-6.547914</v>
+        <v>-6.6391686</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8834493586734593</v>
+        <v>0.9765215096371771</v>
       </c>
       <c r="T92">
-        <v>16.32734511647713</v>
+        <v>18.14149457386348</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01537213222980297</v>
+        <v>0.01520320769980514</v>
       </c>
       <c r="W92">
-        <v>0.2321752512202125</v>
+        <v>0.232215083624386</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06148852891921186</v>
+        <v>0.06081283079922051</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9121,22 +9121,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2992026619655371</v>
+        <v>0.3011026619655371</v>
       </c>
       <c r="C93">
-        <v>-30.62361469197912</v>
+        <v>-31.26017290256838</v>
       </c>
       <c r="D93">
-        <v>16.19938530802088</v>
+        <v>16.07882709743162</v>
       </c>
       <c r="E93">
-        <v>33.056</v>
+        <v>33.572</v>
       </c>
       <c r="F93">
-        <v>46.956</v>
+        <v>47.472</v>
       </c>
       <c r="G93">
         <v>0.133</v>
@@ -9157,37 +9157,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M93">
-        <v>11.0722248</v>
+        <v>11.1938976</v>
       </c>
       <c r="N93">
-        <v>-10.39889146666667</v>
+        <v>-10.52056426666667</v>
       </c>
       <c r="O93">
-        <v>-2.599722866666667</v>
+        <v>-2.630141066666667</v>
       </c>
       <c r="P93">
-        <v>-7.7991686</v>
+        <v>-7.890423200000001</v>
       </c>
       <c r="Q93">
-        <v>-6.6391686</v>
+        <v>-6.730423200000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9765215096371771</v>
+        <v>1.092861698341825</v>
       </c>
       <c r="T93">
-        <v>18.14149457386348</v>
+        <v>20.40918139559642</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01520320769980514</v>
+        <v>0.01503795544219856</v>
       </c>
       <c r="W93">
-        <v>0.232215083624386</v>
+        <v>0.2322540501067296</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06081283079922051</v>
+        <v>0.0601518217687943</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9203,22 +9203,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3011026619655371</v>
+        <v>0.3030026619655372</v>
       </c>
       <c r="C94">
-        <v>-31.26017290256838</v>
+        <v>-31.89494994496624</v>
       </c>
       <c r="D94">
-        <v>16.07882709743162</v>
+        <v>15.96005005503377</v>
       </c>
       <c r="E94">
-        <v>33.572</v>
+        <v>34.08800000000001</v>
       </c>
       <c r="F94">
-        <v>47.472</v>
+        <v>47.98800000000001</v>
       </c>
       <c r="G94">
         <v>0.133</v>
@@ -9239,37 +9239,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M94">
-        <v>11.1938976</v>
+        <v>11.3155704</v>
       </c>
       <c r="N94">
-        <v>-10.52056426666667</v>
+        <v>-10.64223706666667</v>
       </c>
       <c r="O94">
-        <v>-2.630141066666667</v>
+        <v>-2.660559266666667</v>
       </c>
       <c r="P94">
-        <v>-7.890423200000001</v>
+        <v>-7.981677800000002</v>
       </c>
       <c r="Q94">
-        <v>-6.730423200000001</v>
+        <v>-6.821677800000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.092861698341825</v>
+        <v>1.242441940962085</v>
       </c>
       <c r="T94">
-        <v>20.40918139559642</v>
+        <v>23.32477873782448</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01503795544219856</v>
+        <v>0.01487625699658352</v>
       </c>
       <c r="W94">
-        <v>0.2322540501067296</v>
+        <v>0.2322921786002056</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0601518217687943</v>
+        <v>0.05950502798633406</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9285,22 +9285,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3030026619655372</v>
+        <v>0.3049026619655372</v>
       </c>
       <c r="C95">
-        <v>-31.89494994496624</v>
+        <v>-32.52798500309542</v>
       </c>
       <c r="D95">
-        <v>15.96005005503377</v>
+        <v>15.84301499690458</v>
       </c>
       <c r="E95">
-        <v>34.08800000000001</v>
+        <v>34.60400000000001</v>
       </c>
       <c r="F95">
-        <v>47.98800000000001</v>
+        <v>48.504</v>
       </c>
       <c r="G95">
         <v>0.133</v>
@@ -9321,37 +9321,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M95">
-        <v>11.3155704</v>
+        <v>11.4372432</v>
       </c>
       <c r="N95">
-        <v>-10.64223706666667</v>
+        <v>-10.76390986666667</v>
       </c>
       <c r="O95">
-        <v>-2.660559266666667</v>
+        <v>-2.690977466666667</v>
       </c>
       <c r="P95">
-        <v>-7.981677800000002</v>
+        <v>-8.072932400000001</v>
       </c>
       <c r="Q95">
-        <v>-6.821677800000002</v>
+        <v>-6.912932400000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.242441940962085</v>
+        <v>1.441882264455767</v>
       </c>
       <c r="T95">
-        <v>23.32477873782448</v>
+        <v>27.21224186079523</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01487625699658352</v>
+        <v>0.01471799894342837</v>
       </c>
       <c r="W95">
-        <v>0.2322921786002056</v>
+        <v>0.2323294958491396</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05950502798633406</v>
+        <v>0.05887199577371349</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9367,22 +9367,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3049026619655372</v>
+        <v>0.3068026619655372</v>
       </c>
       <c r="C96">
-        <v>-32.52798500309542</v>
+        <v>-33.15931611990256</v>
       </c>
       <c r="D96">
-        <v>15.84301499690458</v>
+        <v>15.72768388009745</v>
       </c>
       <c r="E96">
-        <v>34.60400000000001</v>
+        <v>35.12</v>
       </c>
       <c r="F96">
-        <v>48.504</v>
+        <v>49.02</v>
       </c>
       <c r="G96">
         <v>0.133</v>
@@ -9403,37 +9403,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M96">
-        <v>11.4372432</v>
+        <v>11.558916</v>
       </c>
       <c r="N96">
-        <v>-10.76390986666667</v>
+        <v>-10.88558266666667</v>
       </c>
       <c r="O96">
-        <v>-2.690977466666667</v>
+        <v>-2.721395666666667</v>
       </c>
       <c r="P96">
-        <v>-8.072932400000001</v>
+        <v>-8.164187000000002</v>
       </c>
       <c r="Q96">
-        <v>-6.912932400000001</v>
+        <v>-7.004187000000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.441882264455767</v>
+        <v>1.721098717346921</v>
       </c>
       <c r="T96">
-        <v>27.21224186079523</v>
+        <v>32.6546902329543</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01471799894342837</v>
+        <v>0.01456307263876071</v>
       </c>
       <c r="W96">
-        <v>0.2323294958491396</v>
+        <v>0.2323660274717803</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.05887199577371349</v>
+        <v>0.05825229055504288</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9449,22 +9449,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3068026619655372</v>
+        <v>0.3087026619655372</v>
       </c>
       <c r="C97">
-        <v>-33.15931611990256</v>
+        <v>-33.78898023858729</v>
       </c>
       <c r="D97">
-        <v>15.72768388009745</v>
+        <v>15.61401976141271</v>
       </c>
       <c r="E97">
-        <v>35.12</v>
+        <v>35.63600000000001</v>
       </c>
       <c r="F97">
-        <v>49.02</v>
+        <v>49.53600000000001</v>
       </c>
       <c r="G97">
         <v>0.133</v>
@@ -9485,37 +9485,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M97">
-        <v>11.558916</v>
+        <v>11.6805888</v>
       </c>
       <c r="N97">
-        <v>-10.88558266666667</v>
+        <v>-11.00725546666667</v>
       </c>
       <c r="O97">
-        <v>-2.721395666666667</v>
+        <v>-2.751813866666667</v>
       </c>
       <c r="P97">
-        <v>-8.164187000000002</v>
+        <v>-8.255441600000001</v>
       </c>
       <c r="Q97">
-        <v>-7.004187000000002</v>
+        <v>-7.095441600000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.721098717346921</v>
+        <v>2.139923396683652</v>
       </c>
       <c r="T97">
-        <v>32.6546902329543</v>
+        <v>40.8183627911929</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01456307263876071</v>
+        <v>0.01441137396544028</v>
       </c>
       <c r="W97">
-        <v>0.2323660274717803</v>
+        <v>0.2324017980189492</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05825229055504288</v>
+        <v>0.05764549586176115</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9531,22 +9531,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3087026619655371</v>
+        <v>0.3106026619655372</v>
       </c>
       <c r="C98">
-        <v>-33.78898023858729</v>
+        <v>-34.41701324205666</v>
       </c>
       <c r="D98">
-        <v>15.61401976141271</v>
+        <v>15.50198675794334</v>
       </c>
       <c r="E98">
-        <v>35.636</v>
+        <v>36.152</v>
       </c>
       <c r="F98">
-        <v>49.536</v>
+        <v>50.052</v>
       </c>
       <c r="G98">
         <v>0.133</v>
@@ -9567,37 +9567,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M98">
-        <v>11.6805888</v>
+        <v>11.8022616</v>
       </c>
       <c r="N98">
-        <v>-11.00725546666667</v>
+        <v>-11.12892826666667</v>
       </c>
       <c r="O98">
-        <v>-2.751813866666667</v>
+        <v>-2.782232066666666</v>
       </c>
       <c r="P98">
-        <v>-8.255441600000001</v>
+        <v>-8.3466962</v>
       </c>
       <c r="Q98">
-        <v>-7.095441600000001</v>
+        <v>-7.1866962</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.139923396683646</v>
+        <v>2.837964528911529</v>
       </c>
       <c r="T98">
-        <v>40.81836279119278</v>
+        <v>54.42448372159038</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01441137396544028</v>
+        <v>0.01426280309981719</v>
       </c>
       <c r="W98">
-        <v>0.2324017980189492</v>
+        <v>0.2324368310290631</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05764549586176115</v>
+        <v>0.0570512123992688</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9613,22 +9613,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3106026619655372</v>
+        <v>0.3125026619655371</v>
       </c>
       <c r="C99">
-        <v>-34.41701324205666</v>
+        <v>-35.04344999069285</v>
       </c>
       <c r="D99">
-        <v>15.50198675794334</v>
+        <v>15.39155000930715</v>
       </c>
       <c r="E99">
-        <v>36.152</v>
+        <v>36.668</v>
       </c>
       <c r="F99">
-        <v>50.052</v>
+        <v>50.568</v>
       </c>
       <c r="G99">
         <v>0.133</v>
@@ -9649,37 +9649,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M99">
-        <v>11.8022616</v>
+        <v>11.9239344</v>
       </c>
       <c r="N99">
-        <v>-11.12892826666667</v>
+        <v>-11.25060106666667</v>
       </c>
       <c r="O99">
-        <v>-2.782232066666666</v>
+        <v>-2.812650266666667</v>
       </c>
       <c r="P99">
-        <v>-8.3466962</v>
+        <v>-8.437950799999999</v>
       </c>
       <c r="Q99">
-        <v>-7.1866962</v>
+        <v>-7.277950799999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.837964528911529</v>
+        <v>4.234046793367292</v>
       </c>
       <c r="T99">
-        <v>54.42448372159038</v>
+        <v>81.63672558238555</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01426280309981719</v>
+        <v>0.0141172642926762</v>
       </c>
       <c r="W99">
-        <v>0.2324368310290631</v>
+        <v>0.2324711490797869</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0570512123992688</v>
+        <v>0.05646905717070483</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9695,22 +9695,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3125026619655371</v>
+        <v>0.3144026619655371</v>
       </c>
       <c r="C100">
-        <v>-35.04344999069285</v>
+        <v>-35.66832435851813</v>
       </c>
       <c r="D100">
-        <v>15.39155000930715</v>
+        <v>15.28267564148188</v>
       </c>
       <c r="E100">
-        <v>36.668</v>
+        <v>37.184</v>
       </c>
       <c r="F100">
-        <v>50.568</v>
+        <v>51.084</v>
       </c>
       <c r="G100">
         <v>0.133</v>
@@ -9731,37 +9731,37 @@
         <v>0.6733333333333336</v>
       </c>
       <c r="M100">
-        <v>11.9239344</v>
+        <v>12.0456072</v>
       </c>
       <c r="N100">
-        <v>-11.25060106666667</v>
+        <v>-11.37227386666667</v>
       </c>
       <c r="O100">
-        <v>-2.812650266666667</v>
+        <v>-2.843068466666667</v>
       </c>
       <c r="P100">
-        <v>-8.437950799999999</v>
+        <v>-8.5292054</v>
       </c>
       <c r="Q100">
-        <v>-7.277950799999999</v>
+        <v>-7.3692054</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.234046793367292</v>
+        <v>8.422293586734584</v>
       </c>
       <c r="T100">
-        <v>81.63672558238555</v>
+        <v>163.2734511647711</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0141172642926762</v>
+        <v>0.01397466566345725</v>
       </c>
       <c r="W100">
-        <v>0.2324711490797869</v>
+        <v>0.2325047738365568</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9769,91 +9769,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05646905717070483</v>
+        <v>0.05589866265382903</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3144026619655371</v>
-      </c>
-      <c r="C101">
-        <v>-35.66832435851813</v>
-      </c>
-      <c r="D101">
-        <v>15.28267564148188</v>
-      </c>
-      <c r="E101">
-        <v>37.184</v>
-      </c>
-      <c r="F101">
-        <v>51.084</v>
-      </c>
-      <c r="G101">
-        <v>0.133</v>
-      </c>
-      <c r="H101">
-        <v>37.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="K101">
-        <v>1.16</v>
-      </c>
-      <c r="L101">
-        <v>0.6733333333333336</v>
-      </c>
-      <c r="M101">
-        <v>12.0456072</v>
-      </c>
-      <c r="N101">
-        <v>-11.37227386666667</v>
-      </c>
-      <c r="O101">
-        <v>-2.843068466666667</v>
-      </c>
-      <c r="P101">
-        <v>-8.5292054</v>
-      </c>
-      <c r="Q101">
-        <v>-7.3692054</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.422293586734584</v>
-      </c>
-      <c r="T101">
-        <v>163.2734511647711</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01397466566345725</v>
-      </c>
-      <c r="W101">
-        <v>0.2325047738365568</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05589866265382903</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
